--- a/outputs/3_effective_rates_kendall_2022.xlsx
+++ b/outputs/3_effective_rates_kendall_2022.xlsx
@@ -1598,10 +1598,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.0225682369966408</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.0248731604707136</v>
       </c>
     </row>
     <row r="3">
@@ -1609,10 +1609,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0228628880367817</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0252033640740347</v>
       </c>
     </row>
     <row r="4">
@@ -1620,10 +1620,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.0233800270242094</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.025783111543491</v>
       </c>
     </row>
     <row r="5">
@@ -1631,10 +1631,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.0213873830786354</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.023745764491368</v>
       </c>
     </row>
     <row r="6">
@@ -1642,10 +1642,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.0224002559399774</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.0248750072643418</v>
       </c>
     </row>
     <row r="7">
@@ -1653,10 +1653,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.0222489013879982</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.0247750575261986</v>
       </c>
     </row>
     <row r="8">
@@ -1664,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.0253119275934597</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.0280793253268274</v>
       </c>
     </row>
     <row r="9">
@@ -1675,10 +1675,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.0262829868122523</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.0280959229850929</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.0261984578444701</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.0279208508617413</v>
       </c>
     </row>
     <row r="11">
@@ -1697,10 +1697,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.0262829868122523</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.0280959229850929</v>
       </c>
     </row>
     <row r="12">
@@ -1708,10 +1708,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="13">
@@ -1719,10 +1719,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.0254253558517744</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.0262852615880509</v>
       </c>
     </row>
     <row r="14">
@@ -1730,10 +1730,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.0254253558517744</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.0262852615880509</v>
       </c>
     </row>
     <row r="15">
@@ -1741,10 +1741,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.0255098848195566</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.0264603337114025</v>
       </c>
     </row>
     <row r="16">
@@ -1752,10 +1752,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="17">
@@ -1763,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.027987061869049</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.0289790089014111</v>
       </c>
     </row>
     <row r="18">
@@ -1774,10 +1774,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.027987061869049</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.0289790089014111</v>
       </c>
     </row>
     <row r="19">
@@ -1785,10 +1785,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.0258729204425448</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.02673816177553</v>
       </c>
     </row>
     <row r="20">
@@ -1796,10 +1796,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.0271381054401574</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.0280371676367683</v>
       </c>
     </row>
     <row r="21">
@@ -1807,10 +1807,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.0270114254010961</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.0346800598656811</v>
       </c>
     </row>
     <row r="22">
@@ -1818,10 +1818,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.0266460224352406</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0283737510492204</v>
       </c>
     </row>
     <row r="23">
@@ -1829,10 +1829,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.0280715908368312</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0291540810247627</v>
       </c>
     </row>
     <row r="24">
@@ -1840,10 +1840,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.0258729204425448</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.02673816177553</v>
       </c>
     </row>
     <row r="25">
@@ -1851,10 +1851,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.0284886400981655</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0289790089014111</v>
       </c>
     </row>
     <row r="26">
@@ -1862,10 +1862,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.0279112074328531</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0296727569104586</v>
       </c>
     </row>
     <row r="27">
@@ -1873,10 +1873,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0286799824554892</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0304623799467337</v>
       </c>
     </row>
     <row r="28">
@@ -1884,10 +1884,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.0271381054401574</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0280371676367683</v>
       </c>
     </row>
     <row r="29">
@@ -1895,10 +1895,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0283723800610886</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0291540810247627</v>
       </c>
     </row>
     <row r="30">
@@ -1906,10 +1906,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.0285959852218155</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.0353037939159209</v>
       </c>
     </row>
     <row r="31">
@@ -1917,10 +1917,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.0280715908368312</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.0291540810247627</v>
       </c>
     </row>
     <row r="32">
@@ -1928,10 +1928,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.0291109772793598</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="33">
@@ -1939,10 +1939,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>0.0271678331435226</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.0280371676367683</v>
       </c>
     </row>
     <row r="34">
@@ -1950,10 +1950,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.0282819941119465</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.0291540810247627</v>
       </c>
     </row>
     <row r="35">
@@ -1961,10 +1961,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.029613467852163</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.0315792933347281</v>
       </c>
     </row>
     <row r="36">
@@ -1972,10 +1972,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.0299625841706482</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.0319590493090259</v>
       </c>
     </row>
     <row r="37">
@@ -1983,10 +1983,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.0271840347831824</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.028087168378267</v>
       </c>
     </row>
     <row r="38">
@@ -1994,10 +1994,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.029613467852163</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.0315792933347281</v>
       </c>
     </row>
     <row r="39">
@@ -2005,10 +2005,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>0.0298238711272783</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.0315792933347281</v>
       </c>
     </row>
     <row r="40">
@@ -2016,10 +2016,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="41">
@@ -2027,10 +2027,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.0285750004423701</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.0289790089014111</v>
       </c>
     </row>
     <row r="42">
@@ -2038,10 +2038,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>0.0290237993118597</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.0289790089014111</v>
       </c>
     </row>
     <row r="43">
@@ -2049,10 +2049,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="44">
@@ -2060,10 +2060,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.0270114254010961</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.119724527896064</v>
       </c>
     </row>
     <row r="45">
@@ -2071,10 +2071,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.120523334069655</v>
       </c>
     </row>
     <row r="46">
@@ -2082,10 +2082,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="47">
@@ -2093,10 +2093,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.0285959852218155</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0353037939159209</v>
       </c>
     </row>
     <row r="48">
@@ -2104,10 +2104,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.0262829868122523</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0280959229850929</v>
       </c>
     </row>
     <row r="49">
@@ -2115,10 +2115,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.0286805141895977</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0354788660392725</v>
       </c>
     </row>
     <row r="50">
@@ -2126,10 +2126,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>0.0278287643242651</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.029763305136473</v>
       </c>
     </row>
     <row r="51">
@@ -2137,10 +2137,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>0.0273836441636216</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.029356861911686</v>
       </c>
     </row>
     <row r="52">
@@ -2148,10 +2148,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>0.0273423674074653</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.0293181800691816</v>
       </c>
     </row>
     <row r="53">
@@ -2159,10 +2159,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>0.0263713081886727</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0293015824109161</v>
       </c>
     </row>
     <row r="54">
@@ -2170,10 +2170,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.0229660538472392</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0252339025940441</v>
       </c>
     </row>
     <row r="55">
@@ -2181,10 +2181,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.0230073306033955</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0252725844365484</v>
       </c>
     </row>
     <row r="56">
@@ -2192,10 +2192,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>0.023452450764039</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.0256790276613355</v>
       </c>
     </row>
     <row r="57">
@@ -2203,10 +2203,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>0.0233019816435364</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.0256027880398695</v>
       </c>
     </row>
     <row r="58">
@@ -2214,10 +2214,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>0.0235054416515641</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>0.0257628576254739</v>
       </c>
     </row>
     <row r="59">
@@ -2225,10 +2225,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>0.0238191206309641</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.0261825355093258</v>
       </c>
     </row>
     <row r="60">
@@ -2236,10 +2236,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>0.0231407334165222</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>0.0252136331206617</v>
       </c>
     </row>
     <row r="61">
@@ -2247,10 +2247,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>0.0227361124044434</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.0247473911261845</v>
       </c>
     </row>
     <row r="62">
@@ -2258,10 +2258,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>0.0221983084291296</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.0240995761854433</v>
       </c>
     </row>
     <row r="63">
@@ -2269,10 +2269,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>0.0227773891605997</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.0247860729686889</v>
       </c>
     </row>
     <row r="64">
@@ -2280,10 +2280,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>0.0229660538472392</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.0252339025940441</v>
       </c>
     </row>
     <row r="65">
@@ -2291,10 +2291,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>0.0235054416515641</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.0257628576254739</v>
       </c>
     </row>
     <row r="66">
@@ -2302,10 +2302,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.0302262917016105</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.0371462481906526</v>
       </c>
     </row>
     <row r="67">
@@ -2313,10 +2313,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>0.029781171540967</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.0367398049658656</v>
       </c>
     </row>
     <row r="68">
@@ -2324,10 +2324,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.0247874671603771</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.0319719815348492</v>
       </c>
     </row>
     <row r="69">
@@ -2335,10 +2335,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>0.0227361124044434</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>0.0247473911261845</v>
       </c>
     </row>
     <row r="70">
@@ -2346,10 +2346,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>0.0267871917512852</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>0.0286098941060804</v>
       </c>
     </row>
     <row r="71">
@@ -2357,10 +2357,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>0.0267026627835029</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>0.0284348219827288</v>
       </c>
     </row>
     <row r="72">
@@ -2368,10 +2368,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>0.0291847191286305</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>0.03599283716026</v>
       </c>
     </row>
     <row r="73">
@@ -2379,10 +2379,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.0262478039469603</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>0.0280809390746505</v>
       </c>
     </row>
     <row r="74">
@@ -2390,10 +2390,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>0.0224108781910591</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>0.0245256166309429</v>
       </c>
     </row>
     <row r="75">
@@ -2401,10 +2401,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>0.0251607857681711</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>0.0260096096727634</v>
       </c>
     </row>
     <row r="76">
@@ -2412,10 +2412,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>0.0267871917512852</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>0.0286098941060804</v>
       </c>
     </row>
     <row r="77">
@@ -2423,10 +2423,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>0.0291847191286305</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.03599283716026</v>
       </c>
     </row>
     <row r="78">
@@ -2434,10 +2434,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.029780406707659</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.03599283716026</v>
       </c>
     </row>
     <row r="79">
@@ -2445,10 +2445,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>0.0291847191286305</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>0.03599283716026</v>
       </c>
     </row>
     <row r="80">
@@ -2456,10 +2456,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.0291847191286305</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.03599283716026</v>
       </c>
     </row>
     <row r="81">
@@ -2467,10 +2467,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>0.0223328751750202</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.0243710257064939</v>
       </c>
     </row>
     <row r="82">
@@ -2478,10 +2478,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>0.0232165003108924</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.0254759112920247</v>
       </c>
     </row>
     <row r="83">
@@ -2489,10 +2489,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.0217585072889068</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.023940225294264</v>
       </c>
     </row>
     <row r="84">
@@ -2500,10 +2500,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.0054870913939246</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.00596367054916025</v>
       </c>
     </row>
     <row r="85">
@@ -2511,10 +2511,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>0.0141254608817046</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.0156771063323512</v>
       </c>
     </row>
     <row r="86">
@@ -2522,10 +2522,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>0.0270534260667935</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.0290312337357323</v>
       </c>
     </row>
     <row r="87">
@@ -2533,10 +2533,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>0.025595433044808</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.0274955477379716</v>
       </c>
     </row>
     <row r="88">
@@ -2544,10 +2544,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>0.0222558887252209</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.0243013700505984</v>
       </c>
     </row>
     <row r="89">
@@ -2555,10 +2555,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>0.025595433044808</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.0274955477379716</v>
       </c>
     </row>
     <row r="90">
@@ -2566,10 +2566,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>0.0270534260667935</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.0290312337357323</v>
       </c>
     </row>
     <row r="91">
@@ -2577,10 +2577,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>0.0215905262322435</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.0239420720878921</v>
       </c>
     </row>
     <row r="92">
@@ -2588,10 +2588,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>0.0224520445416062</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.0249713651227227</v>
       </c>
     </row>
     <row r="93">
@@ -2599,10 +2599,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.022676627188918</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.0248629360297674</v>
       </c>
     </row>
     <row r="94">
@@ -2610,10 +2610,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>0.025273392832737</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.0281521848147557</v>
       </c>
     </row>
     <row r="95">
@@ -2621,10 +2621,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.0247355888574232</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.0275043698740146</v>
       </c>
     </row>
     <row r="96">
@@ -2632,10 +2632,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.0277749656716886</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.030965148638435</v>
       </c>
     </row>
     <row r="97">
@@ -2643,10 +2643,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.0277749656716886</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.030965148638435</v>
       </c>
     </row>
     <row r="98">
@@ -2654,10 +2654,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.0274288785380384</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.0293961160556385</v>
       </c>
     </row>
     <row r="99">
@@ -2665,10 +2665,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.0269424816212386</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.0289509909883471</v>
       </c>
     </row>
     <row r="100">
@@ -2676,10 +2676,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>0.0226891873368616</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.00741911379953578</v>
       </c>
     </row>
     <row r="101">
@@ -2687,10 +2687,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.0213508139570775</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.023298519777714</v>
       </c>
     </row>
     <row r="102">
@@ -2698,10 +2698,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>0.0208130099817638</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.0226507048369729</v>
       </c>
     </row>
     <row r="103">
@@ -2709,10 +2709,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>0.024865807725258</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.0269992897339849</v>
       </c>
     </row>
     <row r="104">
@@ -2720,10 +2720,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>0.0236558627878499</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.0257010371693499</v>
       </c>
     </row>
     <row r="105">
@@ -2731,10 +2731,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>0.0294440544601902</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.0317639548120264</v>
       </c>
     </row>
     <row r="106">
@@ -2742,10 +2742,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>0.0266312253336656</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>0.0284817432457866</v>
       </c>
     </row>
     <row r="107">
@@ -2753,10 +2753,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>0.0265466963658834</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>0.028306671122435</v>
       </c>
     </row>
     <row r="108">
@@ -2764,10 +2764,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.0260918375293407</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>0.0279527882143568</v>
       </c>
     </row>
     <row r="109">
@@ -2775,10 +2775,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>0.0241486566505862</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>0.0264427016632798</v>
       </c>
     </row>
     <row r="110">
@@ -2786,10 +2786,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>0.022235489500349</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>0.0243114444345779</v>
       </c>
     </row>
     <row r="111">
@@ -2797,10 +2797,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>0.0200929442867106</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>0.0219941745993932</v>
       </c>
     </row>
     <row r="112">
@@ -2808,10 +2808,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>0.0257739005099868</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>0.0268381147732452</v>
       </c>
     </row>
     <row r="113">
@@ -2819,10 +2819,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>0.0250048193505516</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>0.0258814588124696</v>
       </c>
     </row>
     <row r="114">
@@ -2830,10 +2830,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>0.0250893483183338</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>0.0260565309358212</v>
       </c>
     </row>
     <row r="115">
@@ -2841,10 +2841,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>0.0244654315462267</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>0.0253525037810398</v>
       </c>
     </row>
     <row r="116">
@@ -2852,10 +2852,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>0.0252345127056619</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>0.0263091597418154</v>
       </c>
     </row>
     <row r="117">
@@ -2863,10 +2863,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>0.0245499605140089</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.0255275759043914</v>
       </c>
     </row>
     <row r="118">
@@ -2874,10 +2874,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>0.0230919674920234</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>0.0239918899066306</v>
       </c>
     </row>
     <row r="119">
@@ -2885,10 +2885,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>0.0233990418975164</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>0.0256184311537578</v>
       </c>
     </row>
     <row r="120">
@@ -2896,10 +2896,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>0.0292486042040926</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>0.0304830780268085</v>
       </c>
     </row>
     <row r="121">
@@ -2907,10 +2907,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>0.0236762331742062</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>0.0258677787906279</v>
       </c>
     </row>
     <row r="122">
@@ -2918,10 +2918,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>0.0270387793708002</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>0.027970087709983</v>
       </c>
     </row>
     <row r="123">
@@ -2929,10 +2929,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>0.027147679855899</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>0.0284404169705173</v>
       </c>
     </row>
     <row r="124">
@@ -2940,10 +2940,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>0.024425847927276</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>0.0266920493001499</v>
       </c>
     </row>
     <row r="125">
@@ -2951,10 +2951,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>0.0278145490339317</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>0.0283944491292952</v>
       </c>
     </row>
     <row r="126">
@@ -2962,10 +2962,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.0250257527773638</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>0.0266920493001499</v>
       </c>
     </row>
     <row r="127">
@@ -2973,10 +2973,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>0.0285806563861321</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>0.0303953000199483</v>
       </c>
     </row>
     <row r="128">
@@ -2984,10 +2984,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>0.0286651853539143</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>0.0305703721433</v>
       </c>
     </row>
     <row r="129">
@@ -2995,10 +2995,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>0.0242658368293401</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>0.0239918899066306</v>
       </c>
     </row>
     <row r="130">
@@ -3006,10 +3006,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>0.0262700043481642</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>0.0271804646737079</v>
       </c>
     </row>
     <row r="131">
@@ -3017,10 +3017,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>0.0228353943504368</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>0.0243114444345779</v>
       </c>
     </row>
     <row r="132">
@@ -3028,10 +3028,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>0.0265426755326229</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>0.0276277378095203</v>
       </c>
     </row>
     <row r="133">
@@ -3039,10 +3039,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>0.0263738053600745</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>0.0268381147732452</v>
       </c>
     </row>
     <row r="134">
@@ -3050,10 +3050,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>0.0275719344401459</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>0.0276161464609953</v>
       </c>
     </row>
     <row r="135">
@@ -3061,10 +3061,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>0.024572911234833</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>0.0256184311537578</v>
       </c>
     </row>
     <row r="136">
@@ -3072,10 +3072,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>0.0280247759826766</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>0.0286897646073873</v>
       </c>
     </row>
     <row r="137">
@@ -3083,10 +3083,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.0279642589369138</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>0.0292187196388172</v>
       </c>
     </row>
     <row r="138">
@@ -3094,10 +3094,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.0272556948232414</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>0.0277331086466118</v>
       </c>
     </row>
     <row r="139">
@@ -3105,10 +3105,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>0.0285641637870015</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>0.0292187196388172</v>
       </c>
     </row>
     <row r="140">
@@ -3116,10 +3116,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.0229851042534188</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>0.0251357149440999</v>
       </c>
     </row>
     <row r="141">
@@ -3127,10 +3127,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.0291138114554777</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>0.0300413587709606</v>
       </c>
     </row>
     <row r="142">
@@ -3138,10 +3138,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>0.0263980651028292</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>0.0276161464609953</v>
       </c>
     </row>
     <row r="143">
@@ -3149,10 +3149,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.0284793299224859</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>0.0305703138023905</v>
       </c>
     </row>
     <row r="144">
@@ -3160,10 +3160,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>0.0296531992598026</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>0.0305703138023905</v>
       </c>
     </row>
     <row r="145">
@@ -3171,10 +3171,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>0.0279834192064801</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>0.0291840721655703</v>
       </c>
     </row>
     <row r="146">
@@ -3182,10 +3182,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.027269955205529</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>0.0290823108878741</v>
       </c>
     </row>
     <row r="147">
@@ -3193,10 +3193,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>0.0271854262377468</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>0.0289072387645225</v>
       </c>
     </row>
     <row r="148">
@@ -3204,10 +3204,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>0.0256435492224149</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>0.0264820264545571</v>
       </c>
     </row>
     <row r="149">
@@ -3215,10 +3215,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>0.0269087342200275</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>0.0277810323157953</v>
       </c>
     </row>
     <row r="150">
@@ -3226,10 +3226,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>0.0269087342200275</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>0.0277810323157953</v>
       </c>
     </row>
     <row r="151">
@@ -3237,10 +3237,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="152">
@@ -3248,10 +3248,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="153">
@@ -3259,10 +3259,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>0.0281933707784306</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>0.0290800793147688</v>
       </c>
     </row>
     <row r="154">
@@ -3270,10 +3270,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>0.0280595906765844</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>0.0269951200809798</v>
       </c>
     </row>
     <row r="155">
@@ -3281,10 +3281,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>0.0281933707784306</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>0.0290800793147688</v>
       </c>
     </row>
     <row r="156">
@@ -3292,10 +3292,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>0.0305549526533888</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>0.0320275777979622</v>
       </c>
     </row>
     <row r="157">
@@ -3303,10 +3303,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>0.0305430681921298</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>0.0319318833448138</v>
       </c>
     </row>
     <row r="158">
@@ -3314,10 +3314,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>0.0305430681921298</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>0.0319318833448138</v>
       </c>
     </row>
     <row r="159">
@@ -3325,10 +3325,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>0.0260911138131854</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>0.0269349266420361</v>
       </c>
     </row>
     <row r="160">
@@ -3336,10 +3336,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.0283494778938847</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>0.0293373666718453</v>
       </c>
     </row>
     <row r="161">
@@ -3347,10 +3347,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>0.0276329908285172</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>0.0293601389520015</v>
       </c>
     </row>
     <row r="162">
@@ -3358,10 +3358,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>0.0261756427809677</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>0.0271099987653877</v>
       </c>
     </row>
     <row r="163">
@@ -3369,10 +3369,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.0305430681921298</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>0.0319318833448138</v>
       </c>
     </row>
     <row r="164">
@@ -3380,10 +3380,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>0.0273860265141632</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="165">
@@ -3391,10 +3391,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>0.0288981758261298</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>0.0306591448132398</v>
       </c>
     </row>
     <row r="166">
@@ -3402,10 +3402,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>0.0281933707784306</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>0.0290800793147688</v>
       </c>
     </row>
     <row r="167">
@@ -3413,10 +3413,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="168">
@@ -3424,10 +3424,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="169">
@@ -3435,10 +3435,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="170">
@@ -3446,10 +3446,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>0.027356298810798</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>0.0282339325032744</v>
       </c>
     </row>
     <row r="171">
@@ -3457,10 +3457,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>0.0281933707784306</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>0.0293335792199745</v>
       </c>
     </row>
     <row r="172">
@@ -3468,10 +3468,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>0.0300540526651797</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>0.0290800793147688</v>
       </c>
     </row>
     <row r="173">
@@ -3479,10 +3479,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.0226283021341386</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>0.0246789717310456</v>
       </c>
     </row>
     <row r="174">
@@ -3490,10 +3490,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>0.0247708473477771</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>0.0269962415662303</v>
       </c>
     </row>
     <row r="175">
@@ -3501,10 +3501,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>0.024338130306901</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>0.0265302595377916</v>
       </c>
     </row>
     <row r="176">
@@ -3512,10 +3512,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>0.0242454338313168</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>0.0263637475072774</v>
       </c>
     </row>
     <row r="177">
@@ -3523,10 +3523,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>0.0259130857227278</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>0.0282428929035654</v>
       </c>
     </row>
     <row r="178">
@@ -3534,10 +3534,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>0.0267779407438412</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>0.0279439284001588</v>
       </c>
     </row>
     <row r="179">
@@ -3545,10 +3545,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>0.0256040714065246</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>0.0279439284001588</v>
       </c>
     </row>
   </sheetData>
@@ -3629,19 +3629,19 @@
         <v>412546671</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1557958833</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>43773258</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>152202096</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="J2" t="n">
         <v>1792352.94</v>
@@ -3662,10 +3662,10 @@
         <v>198</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.000863167326065027</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.00094786367881749</v>
       </c>
     </row>
     <row r="3">
@@ -3682,19 +3682,19 @@
         <v>746236794</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>11487478164</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1116044793</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>369010173</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1885782</v>
       </c>
       <c r="J3" t="n">
         <v>24371870.65</v>
@@ -3715,10 +3715,10 @@
         <v>201</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.00178619209604271</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.00189142733724241</v>
       </c>
     </row>
     <row r="4">
@@ -3735,19 +3735,19 @@
         <v>127519461</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>174505479</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>23920962</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="J4" t="n">
         <v>2582380.83</v>
@@ -3768,10 +3768,10 @@
         <v>204</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.00880635054444336</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.00971158898956277</v>
       </c>
     </row>
     <row r="5">
@@ -3788,19 +3788,19 @@
         <v>126578331</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>137024982</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>16342005</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>304737</v>
       </c>
       <c r="J5" t="n">
         <v>412873.57</v>
@@ -3821,10 +3821,10 @@
         <v>207</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.00166682291554689</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.00185358813235356</v>
       </c>
     </row>
     <row r="6">
@@ -3841,19 +3841,19 @@
         <v>746236794</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>11487478164</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1116044793</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>369010173</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1885782</v>
       </c>
       <c r="J6" t="n">
         <v>6091008.01</v>
@@ -3874,10 +3874,10 @@
         <v>210</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.000446404402845401</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.000472704752397697</v>
       </c>
     </row>
     <row r="7">
@@ -3894,19 +3894,19 @@
         <v>221985594</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>219644325</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>25809369</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3076326</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="J7" t="n">
         <v>2866334.12</v>
@@ -3927,10 +3927,10 @@
         <v>213</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.00684767453017509</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.00758141979966208</v>
       </c>
     </row>
     <row r="8">
@@ -3947,19 +3947,19 @@
         <v>219530178</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>219644325</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>25809369</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3076326</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="J8" t="n">
         <v>257126.93</v>
@@ -3980,10 +3980,10 @@
         <v>216</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.000617390820363786</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.000683545955878853</v>
       </c>
     </row>
     <row r="9">
@@ -4000,13 +4000,13 @@
         <v>115229922</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>96503568</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>13389465</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4033,10 +4033,10 @@
         <v>219</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.00153423436115854</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.00173102182479876</v>
       </c>
     </row>
     <row r="10">
@@ -4053,13 +4053,13 @@
         <v>2476608</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>69287826</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>12280905</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4086,10 +4086,10 @@
         <v>222</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.000294651040140876</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.00033020360332106</v>
       </c>
     </row>
     <row r="11">
@@ -4106,13 +4106,13 @@
         <v>2374068</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>68747031</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>12280905</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4139,10 +4139,10 @@
         <v>225</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.00051713898742769</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.000579747469456286</v>
       </c>
     </row>
     <row r="12">
@@ -4159,13 +4159,13 @@
         <v>94827123</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>45138846</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1888407</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1984512</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -4192,10 +4192,10 @@
         <v>227</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.00863836948777999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.00971343578319092</v>
       </c>
     </row>
     <row r="13">
@@ -4212,13 +4212,13 @@
         <v>153940284</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>99331485</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2392737</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1984512</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4245,10 +4245,10 @@
         <v>229</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.000653950054204868</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.00072434535937983</v>
       </c>
     </row>
     <row r="14">
@@ -4265,13 +4265,13 @@
         <v>2395179</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>18511458</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>910887</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>984171</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>231</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.000861518309362774</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.0010292930348306</v>
       </c>
     </row>
     <row r="15">
@@ -4318,19 +4318,19 @@
         <v>333690123</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>9929519331</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1072271535</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>216808077</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1881846</v>
       </c>
       <c r="J15" t="n">
         <v>16223501.22</v>
@@ -4351,10 +4351,10 @@
         <v>233</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.00140255513038993</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.00147681871024735</v>
       </c>
     </row>
     <row r="16">
@@ -4371,19 +4371,19 @@
         <v>185282631</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3097379202</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>276094710</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>50186316</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>600696</v>
       </c>
       <c r="J16" t="n">
         <v>7597553.22</v>
@@ -4404,10 +4404,10 @@
         <v>235</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.00211194307619038</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.00226003135714058</v>
       </c>
     </row>
     <row r="17">
@@ -4424,13 +4424,13 @@
         <v>84682371</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>972526107</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>111378696</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>77550045</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -4457,10 +4457,10 @@
         <v>237</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.000698029569709022</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.000782208515325892</v>
       </c>
     </row>
     <row r="18">
@@ -4477,19 +4477,19 @@
         <v>38260071</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2781952875</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>297268911</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>34462620</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>600696</v>
       </c>
       <c r="J18" t="n">
         <v>1360494.98</v>
@@ -4510,10 +4510,10 @@
         <v>239</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.000427550455900516</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.000463063639253514</v>
       </c>
     </row>
     <row r="19">
@@ -4530,13 +4530,13 @@
         <v>71410863</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>822143478</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>92023371</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>66784572</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -4563,10 +4563,10 @@
         <v>242</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.0184392528623818</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.0207330710152199</v>
       </c>
     </row>
     <row r="20">
@@ -4583,19 +4583,19 @@
         <v>183080820</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3164234043</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>284067594</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>50186316</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>600696</v>
       </c>
       <c r="J20" t="n">
         <v>73776084.91</v>
@@ -4616,10 +4616,10 @@
         <v>244</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.0201083416508834</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.0215318771888113</v>
       </c>
     </row>
     <row r="21">
@@ -4636,16 +4636,16 @@
         <v>88864752</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>5270135211</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>658107483</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>75361467</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4669,10 +4669,10 @@
         <v>246</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.00202741410840816</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.00208495923378897</v>
       </c>
     </row>
     <row r="22">
@@ -4689,13 +4689,13 @@
         <v>2301084</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1614556152</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>201865650</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>45233886</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -4742,13 +4742,13 @@
         <v>14255829</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1972374195</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>251008608</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>47779668</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -4775,10 +4775,10 @@
         <v>250</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.00239752737734539</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.00738294305417961</v>
       </c>
     </row>
     <row r="24">
@@ -4795,16 +4795,16 @@
         <v>69555051</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>5736146493</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>656603817</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>75361467</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -4828,10 +4828,10 @@
         <v>252</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.000768775022636089</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.000789623036275037</v>
       </c>
     </row>
     <row r="25">
@@ -4848,19 +4848,19 @@
         <v>127960221</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5875403397</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>675340206</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>75361467</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>980349</v>
       </c>
       <c r="J25" t="n">
         <v>125311007.49</v>
@@ -4881,10 +4881,10 @@
         <v>254</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.0185664646355516</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.019106664878846</v>
       </c>
     </row>
     <row r="26">
@@ -4901,13 +4901,13 @@
         <v>1899642</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5518009515</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>655596894</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>74986731</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -4954,13 +4954,13 @@
         <v>1015320</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>977167956</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>151919649</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8981619</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -4987,10 +4987,10 @@
         <v>259</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.00128463655840309</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.00129904699897343</v>
       </c>
     </row>
     <row r="28">
@@ -5007,10 +5007,10 @@
         <v>588960</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>843980484</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>40186497</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5040,10 +5040,10 @@
         <v>262</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.00127706945887152</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.0013947003143867</v>
       </c>
     </row>
     <row r="29">
@@ -5060,13 +5060,13 @@
         <v>6159747</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3200854203</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>461384679</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>22944750</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>264</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>0.000447564590770476</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.000452900187479067</v>
       </c>
     </row>
     <row r="30">
@@ -5113,16 +5113,16 @@
         <v>55262724</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5147209074</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>641719428</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>75323934</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -5146,10 +5146,10 @@
         <v>266</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.00126518499761255</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.00129900586123828</v>
       </c>
     </row>
     <row r="31">
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>118283523</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         <v>269</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.000501578229116493</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>66332097</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>271</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.000300789224257451</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>55755303</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5305,7 +5305,7 @@
         <v>273</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.000430463089762063</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>40534581</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5358,7 +5358,7 @@
         <v>275</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.0000297277033651834</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>185368740</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>277</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.000210403275115319</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -5431,10 +5431,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>78066474</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>124659</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>279</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.000349116318485193</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.000379755974297885</v>
       </c>
     </row>
     <row r="37">
@@ -5484,10 +5484,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4417002</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3371550</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -5517,10 +5517,10 @@
         <v>281</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.0000459293430249749</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>0.0000500007414987172</v>
       </c>
     </row>
     <row r="38">
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>35719854</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>283</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.000587938573321156</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -5590,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>33422985</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -5623,7 +5623,7 @@
         <v>285</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.00103673744281069</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>17103411</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>0.0850444680303829</v>
       </c>
     </row>
     <row r="41">
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5749,19 +5749,19 @@
         <v>79636773</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>168635445</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>8411952</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>13710249</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>304737</v>
       </c>
       <c r="J42" t="n">
         <v>499527.26</v>
@@ -5782,10 +5782,10 @@
         <v>291</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.00197332796791327</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>0.00213044579063358</v>
       </c>
     </row>
     <row r="43">
@@ -5802,13 +5802,13 @@
         <v>86073657</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1020163728</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>92799954</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>66784572</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5835,10 +5835,10 @@
         <v>293</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.0016255461593906</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.00181490628984918</v>
       </c>
     </row>
     <row r="44">
@@ -5855,19 +5855,19 @@
         <v>16736940</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>36260829</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2891604</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>13710249</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>300801</v>
       </c>
       <c r="J44" t="n">
         <v>66693.87</v>
@@ -5888,10 +5888,10 @@
         <v>295</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>0.000985412661139104</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>0.00108168226763603</v>
       </c>
     </row>
     <row r="45">
@@ -5908,10 +5908,10 @@
         <v>574224</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>11432271</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1264173</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>300801</v>
       </c>
       <c r="J45" t="n">
         <v>4956.39</v>
@@ -5941,10 +5941,10 @@
         <v>297</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.000363344255922555</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>0.000427560151972871</v>
       </c>
     </row>
     <row r="46">
@@ -5961,19 +5961,19 @@
         <v>26024775</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>116167149</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>22874121</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>24475722</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>300801</v>
       </c>
       <c r="J46" t="n">
         <v>2786116.47</v>
@@ -5994,10 +5994,10 @@
         <v>299</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.0145166739867224</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.0158794059781782</v>
       </c>
     </row>
     <row r="47">
@@ -6014,13 +6014,13 @@
         <v>15695985</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>38980680</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>19586613</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>24475722</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6047,10 +6047,10 @@
         <v>301</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.00108774218407683</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.00116709134910803</v>
       </c>
     </row>
     <row r="48">
@@ -6067,10 +6067,10 @@
         <v>5243487</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>27899988</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3374775</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -6120,13 +6120,13 @@
         <v>101703255</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>909621060</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>58751862</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>15761229</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6153,10 +6153,10 @@
         <v>305</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.000931755394933358</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>0.000977034760240989</v>
       </c>
     </row>
     <row r="50">
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>35253933</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -6206,7 +6206,7 @@
         <v>307</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.000595687579028416</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -6226,19 +6226,19 @@
         <v>264023916</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1557052677</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>24712071</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>151110282</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>980349</v>
       </c>
       <c r="J51" t="n">
         <v>93929.7</v>
@@ -6259,10 +6259,10 @@
         <v>310</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.0000483118144370911</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>0.0000528979952850477</v>
       </c>
     </row>
     <row r="52">
@@ -6279,13 +6279,13 @@
         <v>79298970</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>57767001</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>7781148</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1984512</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -6312,10 +6312,10 @@
         <v>312</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.0016890657003295</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.00187443142603777</v>
       </c>
     </row>
     <row r="53">
@@ -6438,13 +6438,13 @@
         <v>103240953</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>518547492</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>8036067</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6471,10 +6471,10 @@
         <v>318</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.00972447044445449</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.0106342997250662</v>
       </c>
     </row>
     <row r="56">
@@ -6491,13 +6491,13 @@
         <v>103173753</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>518547492</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>8036067</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>320</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.00704432688684183</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.00770339977637192</v>
       </c>
     </row>
     <row r="57">
@@ -6544,10 +6544,10 @@
         <v>6921654</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>19182483</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>210645</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -6597,13 +6597,13 @@
         <v>80714835</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>969891864</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>107572053</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>77550045</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -6630,10 +6630,10 @@
         <v>324</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.000875412611977535</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.00098104819447325</v>
       </c>
     </row>
     <row r="59">
@@ -6650,13 +6650,13 @@
         <v>8560515</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>742404363</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>84251256</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>63642363</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -6683,10 +6683,10 @@
         <v>326</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>0.00250157283895165</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>0.00281296382367924</v>
       </c>
     </row>
     <row r="60">
@@ -6703,7 +6703,7 @@
         <v>242580</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>332619</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -6736,7 +6736,7 @@
         <v>328</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.0158550473665064</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6756,13 +6756,13 @@
         <v>1299180</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>18651138</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>19463187</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>10644021</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -6789,10 +6789,10 @@
         <v>330</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>0.00284285280608615</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>0.00305033233237702</v>
       </c>
     </row>
     <row r="62">
@@ -6809,13 +6809,13 @@
         <v>1299180</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>18651138</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>19463187</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>10644021</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -6842,10 +6842,10 @@
         <v>332</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>0.00120994493740811</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>0.00129825256463502</v>
       </c>
     </row>
     <row r="63">
@@ -6862,10 +6862,10 @@
         <v>87147966</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>983550435</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>8894856</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>980349</v>
       </c>
       <c r="J63" t="n">
         <v>770333.44</v>
@@ -6895,10 +6895,10 @@
         <v>334</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.000727477162876757</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>0.0007959859046622</v>
       </c>
     </row>
     <row r="64">
@@ -6915,10 +6915,10 @@
         <v>13911093</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1136565360</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>7705104</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -6948,10 +6948,10 @@
         <v>336</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.00396004766501066</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>0.00434860191374445</v>
       </c>
     </row>
     <row r="65">
@@ -6968,10 +6968,10 @@
         <v>6311547</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>755512185</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>7705104</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>338</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.0007496147530698</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>0.000824270509522</v>
       </c>
     </row>
     <row r="66">
@@ -7021,10 +7021,10 @@
         <v>11715471</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>771005661</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>7894065</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -7054,10 +7054,10 @@
         <v>340</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>0.0155674414302387</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>0.0171089495716085</v>
       </c>
     </row>
     <row r="67">
@@ -7074,10 +7074,10 @@
         <v>28509594</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>102022404</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>233136</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>980349</v>
       </c>
       <c r="J67" t="n">
         <v>344500.82</v>
@@ -7107,10 +7107,10 @@
         <v>342</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.00279649526784333</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>0.00304161519456455</v>
       </c>
     </row>
     <row r="68">
@@ -7127,10 +7127,10 @@
         <v>5560188</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>408681732</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>10166061</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -7160,10 +7160,10 @@
         <v>344</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>0.00144074367385719</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>0.00155633435605</v>
       </c>
     </row>
     <row r="69">
@@ -7180,7 +7180,7 @@
         <v>4268814</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>586443</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>346</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.000599904850087732</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         <v>12363150</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>380579112</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
         <v>348</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>0.00117386933731665</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -7286,16 +7286,16 @@
         <v>66668022</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5003820675</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>605938479</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>75323934</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -7319,10 +7319,10 @@
         <v>350</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.000645743826541106</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>0.000659828505759645</v>
       </c>
     </row>
     <row r="72">
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1162458</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -7372,7 +7372,7 @@
         <v>352</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>0.00189363400656196</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -7392,10 +7392,10 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>475871196</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>34825368</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -7425,10 +7425,10 @@
         <v>354</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.00101420561710148</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>0.00110803337383255</v>
       </c>
     </row>
     <row r="74">
@@ -7445,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>475871196</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>34825368</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -7478,10 +7478,10 @@
         <v>356</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>0.00541631748604511</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>0.00591739992524989</v>
       </c>
     </row>
     <row r="75">
@@ -7501,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>74561448</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -7534,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>0.000253499905205704</v>
       </c>
     </row>
     <row r="76">
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>6771711</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -7584,7 +7584,7 @@
         <v>360</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>0.00186068188674915</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -7604,13 +7604,13 @@
         <v>95091951</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>135457800</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>8036067</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -7637,10 +7637,10 @@
         <v>362</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>0.000330328338419788</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>0.000359299885251405</v>
       </c>
     </row>
     <row r="78">
@@ -7657,13 +7657,13 @@
         <v>97576980</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>515735241</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>8036067</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -7690,10 +7690,10 @@
         <v>364</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.00173115077082739</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>0.0018927332212336</v>
       </c>
     </row>
     <row r="79">
@@ -7710,13 +7710,13 @@
         <v>40945749</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>105857325</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>6825324</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -7743,10 +7743,10 @@
         <v>366</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>0.00236377822696729</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>0.00257563316612579</v>
       </c>
     </row>
     <row r="80">
@@ -7763,10 +7763,10 @@
         <v>6434718</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>2984133</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1132359</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7796,10 +7796,10 @@
         <v>368</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>0.00227108175138307</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>0.00240912113561159</v>
       </c>
     </row>
     <row r="81">
@@ -7816,13 +7816,13 @@
         <v>2671770</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>73789638</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>3088227</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -7849,10 +7849,10 @@
         <v>370</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>0.00157495541582681</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>0.00171263336577385</v>
       </c>
     </row>
   </sheetData>
@@ -7909,10 +7909,10 @@
         <v>13911093</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1136565360</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7705104</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -7932,13 +7932,13 @@
         <v>14255829</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1972374195</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>251008608</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>47779668</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6926112</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8387796</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -7993,13 +7993,13 @@
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>16332957</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3052146</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>31566</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="E7"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>844158</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -8037,10 +8037,10 @@
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>10761765</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>50491590</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -8058,10 +8058,10 @@
       </c>
       <c r="D9"/>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2448789</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>10659972</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -8081,13 +8081,13 @@
         <v>115229922</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>96503568</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>13389465</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1091814</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
@@ -8106,19 +8106,19 @@
         <v>38260071</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2781952875</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>297268911</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>34462620</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>600696</v>
       </c>
     </row>
     <row r="12">
@@ -8135,19 +8135,19 @@
         <v>79636773</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>168635445</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>8411952</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>13710249</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>304737</v>
       </c>
     </row>
     <row r="13">
@@ -8164,13 +8164,13 @@
         <v>101703255</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>909621060</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>58751862</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>15761229</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -8191,13 +8191,13 @@
         <v>79298970</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>57767001</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7781148</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1984512</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
@@ -8216,13 +8216,13 @@
         <v>80714835</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>969891864</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>107572053</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>77550045</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8243,15 +8243,15 @@
         <v>87147966</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>983550435</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8894856</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>980349</v>
       </c>
     </row>
     <row r="17">
@@ -8268,16 +8268,16 @@
         <v>66668022</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5003820675</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>605938479</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>75323934</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>433119</v>
       </c>
       <c r="I17"/>
     </row>
@@ -8295,13 +8295,13 @@
         <v>97576980</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>515735241</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>8036067</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>149125770</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/outputs/3_effective_rates_kendall_2022.xlsx
+++ b/outputs/3_effective_rates_kendall_2022.xlsx
@@ -10,12 +10,14 @@
     <sheet name="eff rates - district" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="dists without exts" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="dists without MVs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tcs by category and mv" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="tcs by mv" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
   <si>
     <t xml:space="preserve">tax_code</t>
   </si>
@@ -1254,6 +1256,33 @@
   </si>
   <si>
     <t xml:space="preserve">clerk_SS50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm/open space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
   </si>
 </sst>
 </file>
@@ -8455,4 +8484,6848 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" t="n">
+        <v>61358178</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12676167</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" t="n">
+        <v>95040</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C7" t="n">
+        <v>241521</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12280905</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2374068</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1091814</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" t="n">
+        <v>65243031</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>415</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30269166</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5301960</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>418</v>
+      </c>
+      <c r="C16" t="n">
+        <v>463662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>416</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20843304</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>417</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3075720</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" t="n">
+        <v>644898</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" t="n">
+        <v>290166</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9965169</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>418</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3806643</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>416</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3876606</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>420</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1983672</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7551624</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>415</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22176399</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>419</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1941309</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>421</v>
+      </c>
+      <c r="C31" t="n">
+        <v>600696</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>420</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33" t="n">
+        <v>276235332</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>418</v>
+      </c>
+      <c r="C34" t="n">
+        <v>231840</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>415</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9840</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>420</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>417</v>
+      </c>
+      <c r="C38" t="n">
+        <v>38425581</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>418</v>
+      </c>
+      <c r="C39" t="n">
+        <v>917274</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>416</v>
+      </c>
+      <c r="C40" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>417</v>
+      </c>
+      <c r="C41" t="n">
+        <v>16818312</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>418</v>
+      </c>
+      <c r="C42" t="n">
+        <v>127457052</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>415</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>416</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1771932</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>419</v>
+      </c>
+      <c r="C45" t="n">
+        <v>29937996</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" t="n">
+        <v>895668981</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>418</v>
+      </c>
+      <c r="C47" t="n">
+        <v>164148</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>415</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>416</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1052079</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>419</v>
+      </c>
+      <c r="C50" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
+        <v>420</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>417</v>
+      </c>
+      <c r="C52" t="n">
+        <v>32764161</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>419</v>
+      </c>
+      <c r="C53" t="n">
+        <v>37401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" t="s">
+        <v>418</v>
+      </c>
+      <c r="C54" t="n">
+        <v>70755</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" t="s">
+        <v>418</v>
+      </c>
+      <c r="C55" t="n">
+        <v>42049869</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="s">
+        <v>415</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>416</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6703275</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>419</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2545782</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" t="s">
+        <v>417</v>
+      </c>
+      <c r="C59" t="n">
+        <v>98618367</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" t="s">
+        <v>415</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>416</v>
+      </c>
+      <c r="C61" t="n">
+        <v>337500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>417</v>
+      </c>
+      <c r="C62" t="n">
+        <v>260241</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>418</v>
+      </c>
+      <c r="C63" t="n">
+        <v>40061838</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>417</v>
+      </c>
+      <c r="C65" t="n">
+        <v>167947053</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" t="s">
+        <v>418</v>
+      </c>
+      <c r="C66" t="n">
+        <v>721083</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67" t="s">
+        <v>415</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>416</v>
+      </c>
+      <c r="C68" t="n">
+        <v>139530</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" t="s">
+        <v>417</v>
+      </c>
+      <c r="C69" t="n">
+        <v>236493</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" t="s">
+        <v>418</v>
+      </c>
+      <c r="C70" t="n">
+        <v>393207</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" t="s">
+        <v>416</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1069230</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" t="s">
+        <v>417</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3553089</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" t="s">
+        <v>418</v>
+      </c>
+      <c r="C73" t="n">
+        <v>696513</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>416</v>
+      </c>
+      <c r="C74" t="n">
+        <v>158730</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>417</v>
+      </c>
+      <c r="C75" t="n">
+        <v>53136</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" t="s">
+        <v>416</v>
+      </c>
+      <c r="C76" t="n">
+        <v>11970</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" t="s">
+        <v>417</v>
+      </c>
+      <c r="C77" t="n">
+        <v>364359</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>418</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5876694</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" t="s">
+        <v>415</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s">
+        <v>417</v>
+      </c>
+      <c r="C80" t="n">
+        <v>118283523</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>415</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" t="s">
+        <v>416</v>
+      </c>
+      <c r="C82" t="n">
+        <v>21480</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>418</v>
+      </c>
+      <c r="C83" t="n">
+        <v>15241029</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>416</v>
+      </c>
+      <c r="C84" t="n">
+        <v>389400</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" t="s">
+        <v>417</v>
+      </c>
+      <c r="C85" t="n">
+        <v>38097093</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" t="s">
+        <v>418</v>
+      </c>
+      <c r="C86" t="n">
+        <v>19858950</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87" t="s">
+        <v>415</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88" t="s">
+        <v>416</v>
+      </c>
+      <c r="C88" t="n">
+        <v>224370</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" t="s">
+        <v>417</v>
+      </c>
+      <c r="C89" t="n">
+        <v>213226659</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
+        <v>415</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>417</v>
+      </c>
+      <c r="C91" t="n">
+        <v>66332097</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" t="s">
+        <v>417</v>
+      </c>
+      <c r="C92" t="n">
+        <v>243846</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" t="s">
+        <v>415</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>417</v>
+      </c>
+      <c r="C94" t="n">
+        <v>91261542</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" t="s">
+        <v>417</v>
+      </c>
+      <c r="C95" t="n">
+        <v>55755303</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" t="s">
+        <v>417</v>
+      </c>
+      <c r="C96" t="n">
+        <v>25275795</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>415</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>35</v>
+      </c>
+      <c r="B98" t="s">
+        <v>417</v>
+      </c>
+      <c r="C98" t="n">
+        <v>84316386</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>36</v>
+      </c>
+      <c r="B99" t="s">
+        <v>415</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>36</v>
+      </c>
+      <c r="B100" t="s">
+        <v>416</v>
+      </c>
+      <c r="C100" t="n">
+        <v>239490</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>37</v>
+      </c>
+      <c r="B101" t="s">
+        <v>418</v>
+      </c>
+      <c r="C101" t="n">
+        <v>124659</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" t="s">
+        <v>415</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" t="s">
+        <v>417</v>
+      </c>
+      <c r="C103" t="n">
+        <v>78066474</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>38</v>
+      </c>
+      <c r="B104" t="s">
+        <v>418</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3371550</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>38</v>
+      </c>
+      <c r="B105" t="s">
+        <v>417</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4417002</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" t="s">
+        <v>415</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>39</v>
+      </c>
+      <c r="B107" t="s">
+        <v>417</v>
+      </c>
+      <c r="C107" t="n">
+        <v>45912936</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>415</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>417</v>
+      </c>
+      <c r="C109" t="n">
+        <v>101052354</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>41</v>
+      </c>
+      <c r="B110" t="s">
+        <v>418</v>
+      </c>
+      <c r="C110" t="n">
+        <v>8387796</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" t="s">
+        <v>416</v>
+      </c>
+      <c r="C111" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" t="s">
+        <v>415</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
+        <v>417</v>
+      </c>
+      <c r="C113" t="n">
+        <v>35719854</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s">
+        <v>415</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>43</v>
+      </c>
+      <c r="B115" t="s">
+        <v>417</v>
+      </c>
+      <c r="C115" t="n">
+        <v>33422985</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>44</v>
+      </c>
+      <c r="B116" t="s">
+        <v>417</v>
+      </c>
+      <c r="C116" t="n">
+        <v>106584</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>45</v>
+      </c>
+      <c r="B117" t="s">
+        <v>418</v>
+      </c>
+      <c r="C117" t="n">
+        <v>233985</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>46</v>
+      </c>
+      <c r="B118" t="s">
+        <v>418</v>
+      </c>
+      <c r="C118" t="n">
+        <v>16869426</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>47</v>
+      </c>
+      <c r="B119" t="s">
+        <v>418</v>
+      </c>
+      <c r="C119" t="n">
+        <v>182976</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>47</v>
+      </c>
+      <c r="B120" t="s">
+        <v>415</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>47</v>
+      </c>
+      <c r="B121" t="s">
+        <v>416</v>
+      </c>
+      <c r="C121" t="n">
+        <v>51780</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>47</v>
+      </c>
+      <c r="B122" t="s">
+        <v>417</v>
+      </c>
+      <c r="C122" t="n">
+        <v>199419204</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" t="s">
+        <v>415</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
+        <v>417</v>
+      </c>
+      <c r="C124" t="n">
+        <v>58114461</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>49</v>
+      </c>
+      <c r="B125" t="s">
+        <v>416</v>
+      </c>
+      <c r="C125" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" t="s">
+        <v>418</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>51</v>
+      </c>
+      <c r="B127" t="s">
+        <v>415</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>51</v>
+      </c>
+      <c r="B128" t="s">
+        <v>416</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8172210</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B129" t="s">
+        <v>420</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>51</v>
+      </c>
+      <c r="B130" t="s">
+        <v>417</v>
+      </c>
+      <c r="C130" t="n">
+        <v>13945182</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>52</v>
+      </c>
+      <c r="B131" t="s">
+        <v>416</v>
+      </c>
+      <c r="C131" t="n">
+        <v>868290</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>53</v>
+      </c>
+      <c r="B132" t="s">
+        <v>415</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>53</v>
+      </c>
+      <c r="B133" t="s">
+        <v>416</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2703918</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>53</v>
+      </c>
+      <c r="B134" t="s">
+        <v>420</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>53</v>
+      </c>
+      <c r="B135" t="s">
+        <v>417</v>
+      </c>
+      <c r="C135" t="n">
+        <v>24902982</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>54</v>
+      </c>
+      <c r="B136" t="s">
+        <v>415</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>54</v>
+      </c>
+      <c r="B137" t="s">
+        <v>416</v>
+      </c>
+      <c r="C137" t="n">
+        <v>90930</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>54</v>
+      </c>
+      <c r="B138" t="s">
+        <v>417</v>
+      </c>
+      <c r="C138" t="n">
+        <v>650571</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" t="s">
+        <v>418</v>
+      </c>
+      <c r="C139" t="n">
+        <v>6714</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>55</v>
+      </c>
+      <c r="B140" t="s">
+        <v>415</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>55</v>
+      </c>
+      <c r="B141" t="s">
+        <v>416</v>
+      </c>
+      <c r="C141" t="n">
+        <v>425730</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" t="s">
+        <v>417</v>
+      </c>
+      <c r="C142" t="n">
+        <v>21572397</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>56</v>
+      </c>
+      <c r="B143" t="s">
+        <v>418</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2138859</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>56</v>
+      </c>
+      <c r="B144" t="s">
+        <v>415</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>56</v>
+      </c>
+      <c r="B145" t="s">
+        <v>416</v>
+      </c>
+      <c r="C145" t="n">
+        <v>37682820</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B146" t="s">
+        <v>421</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>56</v>
+      </c>
+      <c r="B147" t="s">
+        <v>420</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>56</v>
+      </c>
+      <c r="B148" t="s">
+        <v>417</v>
+      </c>
+      <c r="C148" t="n">
+        <v>37106661</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>57</v>
+      </c>
+      <c r="B149" t="s">
+        <v>415</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>57</v>
+      </c>
+      <c r="B150" t="s">
+        <v>416</v>
+      </c>
+      <c r="C150" t="n">
+        <v>4007892</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>57</v>
+      </c>
+      <c r="B151" t="s">
+        <v>420</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>57</v>
+      </c>
+      <c r="B152" t="s">
+        <v>417</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1823796</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>58</v>
+      </c>
+      <c r="B153" t="s">
+        <v>415</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>58</v>
+      </c>
+      <c r="B154" t="s">
+        <v>416</v>
+      </c>
+      <c r="C154" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>58</v>
+      </c>
+      <c r="B155" t="s">
+        <v>417</v>
+      </c>
+      <c r="C155" t="n">
+        <v>299274</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>59</v>
+      </c>
+      <c r="B156" t="s">
+        <v>416</v>
+      </c>
+      <c r="C156" t="n">
+        <v>414096</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>59</v>
+      </c>
+      <c r="B157" t="s">
+        <v>420</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>59</v>
+      </c>
+      <c r="B158" t="s">
+        <v>417</v>
+      </c>
+      <c r="C158" t="n">
+        <v>423873</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>60</v>
+      </c>
+      <c r="B159" t="s">
+        <v>415</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>60</v>
+      </c>
+      <c r="B160" t="s">
+        <v>417</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3504000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>61</v>
+      </c>
+      <c r="B161" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1264173</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>61</v>
+      </c>
+      <c r="B162" t="s">
+        <v>415</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>61</v>
+      </c>
+      <c r="B163" t="s">
+        <v>416</v>
+      </c>
+      <c r="C163" t="n">
+        <v>574224</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>61</v>
+      </c>
+      <c r="B164" t="s">
+        <v>421</v>
+      </c>
+      <c r="C164" t="n">
+        <v>300801</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>61</v>
+      </c>
+      <c r="B165" t="s">
+        <v>420</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>61</v>
+      </c>
+      <c r="B166" t="s">
+        <v>417</v>
+      </c>
+      <c r="C166" t="n">
+        <v>11432271</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>62</v>
+      </c>
+      <c r="B167" t="s">
+        <v>418</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1433025</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>62</v>
+      </c>
+      <c r="B168" t="s">
+        <v>415</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>62</v>
+      </c>
+      <c r="B169" t="s">
+        <v>416</v>
+      </c>
+      <c r="C169" t="n">
+        <v>5002209</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>62</v>
+      </c>
+      <c r="B170" t="s">
+        <v>417</v>
+      </c>
+      <c r="C170" t="n">
+        <v>18988212</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>63</v>
+      </c>
+      <c r="B171" t="s">
+        <v>415</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>63</v>
+      </c>
+      <c r="B172" t="s">
+        <v>416</v>
+      </c>
+      <c r="C172" t="n">
+        <v>9922332</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>63</v>
+      </c>
+      <c r="B173" t="s">
+        <v>419</v>
+      </c>
+      <c r="C173" t="n">
+        <v>13710249</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>63</v>
+      </c>
+      <c r="B174" t="s">
+        <v>417</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1972383</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>64</v>
+      </c>
+      <c r="B175" t="s">
+        <v>418</v>
+      </c>
+      <c r="C175" t="n">
+        <v>194406</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>64</v>
+      </c>
+      <c r="B176" t="s">
+        <v>416</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1238175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>64</v>
+      </c>
+      <c r="B177" t="s">
+        <v>417</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3446337</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>65</v>
+      </c>
+      <c r="B178" t="s">
+        <v>418</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3374775</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>65</v>
+      </c>
+      <c r="B179" t="s">
+        <v>415</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>65</v>
+      </c>
+      <c r="B180" t="s">
+        <v>416</v>
+      </c>
+      <c r="C180" t="n">
+        <v>4416009</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>65</v>
+      </c>
+      <c r="B181" t="s">
+        <v>417</v>
+      </c>
+      <c r="C181" t="n">
+        <v>27478362</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>66</v>
+      </c>
+      <c r="B182" t="s">
+        <v>416</v>
+      </c>
+      <c r="C182" t="n">
+        <v>827478</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>67</v>
+      </c>
+      <c r="B183" t="s">
+        <v>415</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>67</v>
+      </c>
+      <c r="B184" t="s">
+        <v>416</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1746228</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>67</v>
+      </c>
+      <c r="B185" t="s">
+        <v>417</v>
+      </c>
+      <c r="C185" t="n">
+        <v>667518</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>68</v>
+      </c>
+      <c r="B186" t="s">
+        <v>416</v>
+      </c>
+      <c r="C186" t="n">
+        <v>21270</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>69</v>
+      </c>
+      <c r="B187" t="s">
+        <v>416</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1515462</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>70</v>
+      </c>
+      <c r="B188" t="s">
+        <v>417</v>
+      </c>
+      <c r="C188" t="n">
+        <v>421626</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>71</v>
+      </c>
+      <c r="B189" t="s">
+        <v>418</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5173416</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>71</v>
+      </c>
+      <c r="B190" t="s">
+        <v>415</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>71</v>
+      </c>
+      <c r="B191" t="s">
+        <v>416</v>
+      </c>
+      <c r="C191" t="n">
+        <v>69809889</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>71</v>
+      </c>
+      <c r="B192" t="s">
+        <v>419</v>
+      </c>
+      <c r="C192" t="n">
+        <v>465339</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>71</v>
+      </c>
+      <c r="B193" t="s">
+        <v>420</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>71</v>
+      </c>
+      <c r="B194" t="s">
+        <v>417</v>
+      </c>
+      <c r="C194" t="n">
+        <v>239306019</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>72</v>
+      </c>
+      <c r="B195" t="s">
+        <v>415</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>72</v>
+      </c>
+      <c r="B196" t="s">
+        <v>416</v>
+      </c>
+      <c r="C196" t="n">
+        <v>547260</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>72</v>
+      </c>
+      <c r="B197" t="s">
+        <v>417</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1835784</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>73</v>
+      </c>
+      <c r="B198" t="s">
+        <v>418</v>
+      </c>
+      <c r="C198" t="n">
+        <v>34521984</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>73</v>
+      </c>
+      <c r="B199" t="s">
+        <v>415</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>73</v>
+      </c>
+      <c r="B200" t="s">
+        <v>416</v>
+      </c>
+      <c r="C200" t="n">
+        <v>456420</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>73</v>
+      </c>
+      <c r="B201" t="s">
+        <v>419</v>
+      </c>
+      <c r="C201" t="n">
+        <v>15264324</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>73</v>
+      </c>
+      <c r="B202" t="s">
+        <v>420</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>73</v>
+      </c>
+      <c r="B203" t="s">
+        <v>417</v>
+      </c>
+      <c r="C203" t="n">
+        <v>592139916</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>74</v>
+      </c>
+      <c r="B204" t="s">
+        <v>418</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1144149</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>74</v>
+      </c>
+      <c r="B205" t="s">
+        <v>415</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>74</v>
+      </c>
+      <c r="B206" t="s">
+        <v>416</v>
+      </c>
+      <c r="C206" t="n">
+        <v>24813783</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>74</v>
+      </c>
+      <c r="B207" t="s">
+        <v>417</v>
+      </c>
+      <c r="C207" t="n">
+        <v>7052328</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>75</v>
+      </c>
+      <c r="B208" t="s">
+        <v>415</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>75</v>
+      </c>
+      <c r="B209" t="s">
+        <v>416</v>
+      </c>
+      <c r="C209" t="n">
+        <v>4170405</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>75</v>
+      </c>
+      <c r="B210" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1158138</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>76</v>
+      </c>
+      <c r="B211" t="s">
+        <v>416</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>76</v>
+      </c>
+      <c r="B212" t="s">
+        <v>417</v>
+      </c>
+      <c r="C212" t="n">
+        <v>10572</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>77</v>
+      </c>
+      <c r="B213" t="s">
+        <v>416</v>
+      </c>
+      <c r="C213" t="n">
+        <v>46482</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>77</v>
+      </c>
+      <c r="B214" t="s">
+        <v>417</v>
+      </c>
+      <c r="C214" t="n">
+        <v>31377</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>78</v>
+      </c>
+      <c r="B215" t="s">
+        <v>418</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4200195</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>78</v>
+      </c>
+      <c r="B216" t="s">
+        <v>415</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>78</v>
+      </c>
+      <c r="B217" t="s">
+        <v>416</v>
+      </c>
+      <c r="C217" t="n">
+        <v>917982</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>78</v>
+      </c>
+      <c r="B218" t="s">
+        <v>417</v>
+      </c>
+      <c r="C218" t="n">
+        <v>14051247</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>79</v>
+      </c>
+      <c r="B219" t="s">
+        <v>415</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>79</v>
+      </c>
+      <c r="B220" t="s">
+        <v>417</v>
+      </c>
+      <c r="C220" t="n">
+        <v>35253933</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>80</v>
+      </c>
+      <c r="B221" t="s">
+        <v>418</v>
+      </c>
+      <c r="C221" t="n">
+        <v>10659972</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>80</v>
+      </c>
+      <c r="B222" t="s">
+        <v>415</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>80</v>
+      </c>
+      <c r="B223" t="s">
+        <v>417</v>
+      </c>
+      <c r="C223" t="n">
+        <v>2448789</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>81</v>
+      </c>
+      <c r="B224" t="s">
+        <v>418</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3052146</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>81</v>
+      </c>
+      <c r="B225" t="s">
+        <v>415</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>81</v>
+      </c>
+      <c r="B226" t="s">
+        <v>419</v>
+      </c>
+      <c r="C226" t="n">
+        <v>31566</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>81</v>
+      </c>
+      <c r="B227" t="s">
+        <v>417</v>
+      </c>
+      <c r="C227" t="n">
+        <v>16332957</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>82</v>
+      </c>
+      <c r="B228" t="s">
+        <v>416</v>
+      </c>
+      <c r="C228" t="n">
+        <v>939954</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>83</v>
+      </c>
+      <c r="B229" t="s">
+        <v>418</v>
+      </c>
+      <c r="C229" t="n">
+        <v>6119709</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>83</v>
+      </c>
+      <c r="B230" t="s">
+        <v>416</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4340820</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>83</v>
+      </c>
+      <c r="B231" t="s">
+        <v>417</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2146719</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>84</v>
+      </c>
+      <c r="B232" t="s">
+        <v>416</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4944009</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>84</v>
+      </c>
+      <c r="B233" t="s">
+        <v>417</v>
+      </c>
+      <c r="C233" t="n">
+        <v>831540</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>85</v>
+      </c>
+      <c r="B234" t="s">
+        <v>416</v>
+      </c>
+      <c r="C234" t="n">
+        <v>214527</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>86</v>
+      </c>
+      <c r="B235" t="s">
+        <v>416</v>
+      </c>
+      <c r="C235" t="n">
+        <v>428190</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>87</v>
+      </c>
+      <c r="B236" t="s">
+        <v>416</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4219869</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>87</v>
+      </c>
+      <c r="B237" t="s">
+        <v>417</v>
+      </c>
+      <c r="C237" t="n">
+        <v>878268</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>88</v>
+      </c>
+      <c r="B238" t="s">
+        <v>418</v>
+      </c>
+      <c r="C238" t="n">
+        <v>670947</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>88</v>
+      </c>
+      <c r="B239" t="s">
+        <v>415</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>88</v>
+      </c>
+      <c r="B240" t="s">
+        <v>416</v>
+      </c>
+      <c r="C240" t="n">
+        <v>9569631</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>88</v>
+      </c>
+      <c r="B241" t="s">
+        <v>417</v>
+      </c>
+      <c r="C241" t="n">
+        <v>5119743</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>89</v>
+      </c>
+      <c r="B242" t="s">
+        <v>416</v>
+      </c>
+      <c r="C242" t="n">
+        <v>5596773</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>89</v>
+      </c>
+      <c r="B243" t="s">
+        <v>417</v>
+      </c>
+      <c r="C243" t="n">
+        <v>2812251</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>90</v>
+      </c>
+      <c r="B244" t="s">
+        <v>418</v>
+      </c>
+      <c r="C244" t="n">
+        <v>210645</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>90</v>
+      </c>
+      <c r="B245" t="s">
+        <v>415</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>90</v>
+      </c>
+      <c r="B246" t="s">
+        <v>416</v>
+      </c>
+      <c r="C246" t="n">
+        <v>6175896</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>90</v>
+      </c>
+      <c r="B247" t="s">
+        <v>417</v>
+      </c>
+      <c r="C247" t="n">
+        <v>19182483</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>91</v>
+      </c>
+      <c r="B248" t="s">
+        <v>416</v>
+      </c>
+      <c r="C248" t="n">
+        <v>745758</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>92</v>
+      </c>
+      <c r="B249" t="s">
+        <v>418</v>
+      </c>
+      <c r="C249" t="n">
+        <v>513858</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>92</v>
+      </c>
+      <c r="B250" t="s">
+        <v>415</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>92</v>
+      </c>
+      <c r="B251" t="s">
+        <v>416</v>
+      </c>
+      <c r="C251" t="n">
+        <v>40891284</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>92</v>
+      </c>
+      <c r="B252" t="s">
+        <v>419</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1000341</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>92</v>
+      </c>
+      <c r="B253" t="s">
+        <v>417</v>
+      </c>
+      <c r="C253" t="n">
+        <v>18249708</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>93</v>
+      </c>
+      <c r="B254" t="s">
+        <v>418</v>
+      </c>
+      <c r="C254" t="n">
+        <v>265989</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>93</v>
+      </c>
+      <c r="B255" t="s">
+        <v>415</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>93</v>
+      </c>
+      <c r="B256" t="s">
+        <v>416</v>
+      </c>
+      <c r="C256" t="n">
+        <v>2105013</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>93</v>
+      </c>
+      <c r="B257" t="s">
+        <v>419</v>
+      </c>
+      <c r="C257" t="n">
+        <v>984171</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>93</v>
+      </c>
+      <c r="B258" t="s">
+        <v>417</v>
+      </c>
+      <c r="C258" t="n">
+        <v>8546289</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>94</v>
+      </c>
+      <c r="B259" t="s">
+        <v>416</v>
+      </c>
+      <c r="C259" t="n">
+        <v>67200</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>95</v>
+      </c>
+      <c r="B260" t="s">
+        <v>418</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3338280</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>95</v>
+      </c>
+      <c r="B261" t="s">
+        <v>415</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>95</v>
+      </c>
+      <c r="B262" t="s">
+        <v>416</v>
+      </c>
+      <c r="C262" t="n">
+        <v>57562824</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>95</v>
+      </c>
+      <c r="B263" t="s">
+        <v>419</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3142209</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>95</v>
+      </c>
+      <c r="B264" t="s">
+        <v>420</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>95</v>
+      </c>
+      <c r="B265" t="s">
+        <v>417</v>
+      </c>
+      <c r="C265" t="n">
+        <v>113182224</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>96</v>
+      </c>
+      <c r="B266" t="s">
+        <v>415</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>96</v>
+      </c>
+      <c r="B267" t="s">
+        <v>416</v>
+      </c>
+      <c r="C267" t="n">
+        <v>305328</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>96</v>
+      </c>
+      <c r="B268" t="s">
+        <v>417</v>
+      </c>
+      <c r="C268" t="n">
+        <v>134352</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>97</v>
+      </c>
+      <c r="B269" t="s">
+        <v>418</v>
+      </c>
+      <c r="C269" t="n">
+        <v>77325144</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>97</v>
+      </c>
+      <c r="B270" t="s">
+        <v>415</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>97</v>
+      </c>
+      <c r="B271" t="s">
+        <v>416</v>
+      </c>
+      <c r="C271" t="n">
+        <v>8505945</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>97</v>
+      </c>
+      <c r="B272" t="s">
+        <v>419</v>
+      </c>
+      <c r="C272" t="n">
+        <v>63642363</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>97</v>
+      </c>
+      <c r="B273" t="s">
+        <v>420</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>97</v>
+      </c>
+      <c r="B274" t="s">
+        <v>417</v>
+      </c>
+      <c r="C274" t="n">
+        <v>702639570</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>98</v>
+      </c>
+      <c r="B275" t="s">
+        <v>418</v>
+      </c>
+      <c r="C275" t="n">
+        <v>6926112</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>99</v>
+      </c>
+      <c r="B276" t="s">
+        <v>415</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>99</v>
+      </c>
+      <c r="B277" t="s">
+        <v>416</v>
+      </c>
+      <c r="C277" t="n">
+        <v>2747895</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>99</v>
+      </c>
+      <c r="B278" t="s">
+        <v>417</v>
+      </c>
+      <c r="C278" t="n">
+        <v>7157862</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>100</v>
+      </c>
+      <c r="B279" t="s">
+        <v>415</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>100</v>
+      </c>
+      <c r="B280" t="s">
+        <v>416</v>
+      </c>
+      <c r="C280" t="n">
+        <v>2007858</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>100</v>
+      </c>
+      <c r="B281" t="s">
+        <v>417</v>
+      </c>
+      <c r="C281" t="n">
+        <v>26774124</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>101</v>
+      </c>
+      <c r="B282" t="s">
+        <v>416</v>
+      </c>
+      <c r="C282" t="n">
+        <v>242580</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>101</v>
+      </c>
+      <c r="B283" t="s">
+        <v>417</v>
+      </c>
+      <c r="C283" t="n">
+        <v>332619</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>102</v>
+      </c>
+      <c r="B284" t="s">
+        <v>418</v>
+      </c>
+      <c r="C284" t="n">
+        <v>395904</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>102</v>
+      </c>
+      <c r="B285" t="s">
+        <v>416</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3819510</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>102</v>
+      </c>
+      <c r="B286" t="s">
+        <v>417</v>
+      </c>
+      <c r="C286" t="n">
+        <v>43032375</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>103</v>
+      </c>
+      <c r="B287" t="s">
+        <v>418</v>
+      </c>
+      <c r="C287" t="n">
+        <v>123426</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>103</v>
+      </c>
+      <c r="B288" t="s">
+        <v>415</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>103</v>
+      </c>
+      <c r="B289" t="s">
+        <v>416</v>
+      </c>
+      <c r="C289" t="n">
+        <v>4169145</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>103</v>
+      </c>
+      <c r="B290" t="s">
+        <v>419</v>
+      </c>
+      <c r="C290" t="n">
+        <v>121452</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>103</v>
+      </c>
+      <c r="B291" t="s">
+        <v>420</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>103</v>
+      </c>
+      <c r="B292" t="s">
+        <v>417</v>
+      </c>
+      <c r="C292" t="n">
+        <v>18222807</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>104</v>
+      </c>
+      <c r="B293" t="s">
+        <v>418</v>
+      </c>
+      <c r="C293" t="n">
+        <v>19463187</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>104</v>
+      </c>
+      <c r="B294" t="s">
+        <v>415</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>104</v>
+      </c>
+      <c r="B295" t="s">
+        <v>416</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1299180</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>104</v>
+      </c>
+      <c r="B296" t="s">
+        <v>419</v>
+      </c>
+      <c r="C296" t="n">
+        <v>10644021</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>104</v>
+      </c>
+      <c r="B297" t="s">
+        <v>417</v>
+      </c>
+      <c r="C297" t="n">
+        <v>18651138</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>105</v>
+      </c>
+      <c r="B298" t="s">
+        <v>415</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>106</v>
+      </c>
+      <c r="B299" t="s">
+        <v>415</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>106</v>
+      </c>
+      <c r="B300" t="s">
+        <v>416</v>
+      </c>
+      <c r="C300" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>106</v>
+      </c>
+      <c r="B301" t="s">
+        <v>417</v>
+      </c>
+      <c r="C301" t="n">
+        <v>39764793</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>107</v>
+      </c>
+      <c r="B302" t="s">
+        <v>418</v>
+      </c>
+      <c r="C302" t="n">
+        <v>106281</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>107</v>
+      </c>
+      <c r="B303" t="s">
+        <v>415</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>107</v>
+      </c>
+      <c r="B304" t="s">
+        <v>416</v>
+      </c>
+      <c r="C304" t="n">
+        <v>4965543</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>107</v>
+      </c>
+      <c r="B305" t="s">
+        <v>417</v>
+      </c>
+      <c r="C305" t="n">
+        <v>26270064</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>108</v>
+      </c>
+      <c r="B306" t="s">
+        <v>416</v>
+      </c>
+      <c r="C306" t="n">
+        <v>12060</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>108</v>
+      </c>
+      <c r="B307" t="s">
+        <v>417</v>
+      </c>
+      <c r="C307" t="n">
+        <v>7362243</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>109</v>
+      </c>
+      <c r="B308" t="s">
+        <v>416</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1264194</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>109</v>
+      </c>
+      <c r="B309" t="s">
+        <v>417</v>
+      </c>
+      <c r="C309" t="n">
+        <v>215838</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>110</v>
+      </c>
+      <c r="B310" t="s">
+        <v>418</v>
+      </c>
+      <c r="C310" t="n">
+        <v>7705104</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>110</v>
+      </c>
+      <c r="B311" t="s">
+        <v>415</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>110</v>
+      </c>
+      <c r="B312" t="s">
+        <v>416</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1185153</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>110</v>
+      </c>
+      <c r="B313" t="s">
+        <v>417</v>
+      </c>
+      <c r="C313" t="n">
+        <v>754079490</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>111</v>
+      </c>
+      <c r="B314" t="s">
+        <v>418</v>
+      </c>
+      <c r="C314" t="n">
+        <v>188961</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>111</v>
+      </c>
+      <c r="B315" t="s">
+        <v>415</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>111</v>
+      </c>
+      <c r="B316" t="s">
+        <v>416</v>
+      </c>
+      <c r="C316" t="n">
+        <v>5844237</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>111</v>
+      </c>
+      <c r="B317" t="s">
+        <v>417</v>
+      </c>
+      <c r="C317" t="n">
+        <v>14985078</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>112</v>
+      </c>
+      <c r="B318" t="s">
+        <v>416</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1084140</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>113</v>
+      </c>
+      <c r="B319" t="s">
+        <v>418</v>
+      </c>
+      <c r="C319" t="n">
+        <v>44175</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>113</v>
+      </c>
+      <c r="B320" t="s">
+        <v>415</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>113</v>
+      </c>
+      <c r="B321" t="s">
+        <v>416</v>
+      </c>
+      <c r="C321" t="n">
+        <v>15067104</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>113</v>
+      </c>
+      <c r="B322" t="s">
+        <v>421</v>
+      </c>
+      <c r="C322" t="n">
+        <v>980349</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>113</v>
+      </c>
+      <c r="B323" t="s">
+        <v>417</v>
+      </c>
+      <c r="C323" t="n">
+        <v>30653025</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B324" t="s">
+        <v>418</v>
+      </c>
+      <c r="C324" t="n">
+        <v>842319</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>114</v>
+      </c>
+      <c r="B325" t="s">
+        <v>416</v>
+      </c>
+      <c r="C325" t="n">
+        <v>17529636</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>114</v>
+      </c>
+      <c r="B326" t="s">
+        <v>417</v>
+      </c>
+      <c r="C326" t="n">
+        <v>51557337</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>115</v>
+      </c>
+      <c r="B327" t="s">
+        <v>415</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>115</v>
+      </c>
+      <c r="B328" t="s">
+        <v>416</v>
+      </c>
+      <c r="C328" t="n">
+        <v>3577692</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>115</v>
+      </c>
+      <c r="B329" t="s">
+        <v>417</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1050381</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>116</v>
+      </c>
+      <c r="B330" t="s">
+        <v>416</v>
+      </c>
+      <c r="C330" t="n">
+        <v>5813295</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>116</v>
+      </c>
+      <c r="B331" t="s">
+        <v>417</v>
+      </c>
+      <c r="C331" t="n">
+        <v>789027</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>117</v>
+      </c>
+      <c r="B332" t="s">
+        <v>415</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>117</v>
+      </c>
+      <c r="B333" t="s">
+        <v>416</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1286880</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>117</v>
+      </c>
+      <c r="B334" t="s">
+        <v>417</v>
+      </c>
+      <c r="C334" t="n">
+        <v>8008953</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>118</v>
+      </c>
+      <c r="B335" t="s">
+        <v>416</v>
+      </c>
+      <c r="C335" t="n">
+        <v>7563750</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>118</v>
+      </c>
+      <c r="B336" t="s">
+        <v>417</v>
+      </c>
+      <c r="C336" t="n">
+        <v>3701583</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>119</v>
+      </c>
+      <c r="B337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C337" t="n">
+        <v>8016</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>119</v>
+      </c>
+      <c r="B338" t="s">
+        <v>416</v>
+      </c>
+      <c r="C338" t="n">
+        <v>4815495</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>119</v>
+      </c>
+      <c r="B339" t="s">
+        <v>417</v>
+      </c>
+      <c r="C339" t="n">
+        <v>2701305</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>120</v>
+      </c>
+      <c r="B340" t="s">
+        <v>415</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>120</v>
+      </c>
+      <c r="B341" t="s">
+        <v>417</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1148100</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>121</v>
+      </c>
+      <c r="B342" t="s">
+        <v>415</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>121</v>
+      </c>
+      <c r="B343" t="s">
+        <v>416</v>
+      </c>
+      <c r="C343" t="n">
+        <v>108480</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>121</v>
+      </c>
+      <c r="B344" t="s">
+        <v>417</v>
+      </c>
+      <c r="C344" t="n">
+        <v>47111649</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>122</v>
+      </c>
+      <c r="B345" t="s">
+        <v>415</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>122</v>
+      </c>
+      <c r="B346" t="s">
+        <v>416</v>
+      </c>
+      <c r="C346" t="n">
+        <v>139800</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>123</v>
+      </c>
+      <c r="B347" t="s">
+        <v>415</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>123</v>
+      </c>
+      <c r="B348" t="s">
+        <v>416</v>
+      </c>
+      <c r="C348" t="n">
+        <v>115920</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>123</v>
+      </c>
+      <c r="B349" t="s">
+        <v>417</v>
+      </c>
+      <c r="C349" t="n">
+        <v>24128319</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>124</v>
+      </c>
+      <c r="B350" t="s">
+        <v>415</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>124</v>
+      </c>
+      <c r="B351" t="s">
+        <v>416</v>
+      </c>
+      <c r="C351" t="n">
+        <v>306720</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>124</v>
+      </c>
+      <c r="B352" t="s">
+        <v>417</v>
+      </c>
+      <c r="C352" t="n">
+        <v>465972</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>125</v>
+      </c>
+      <c r="B353" t="s">
+        <v>416</v>
+      </c>
+      <c r="C353" t="n">
+        <v>957375</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>125</v>
+      </c>
+      <c r="B354" t="s">
+        <v>417</v>
+      </c>
+      <c r="C354" t="n">
+        <v>380280</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>126</v>
+      </c>
+      <c r="B355" t="s">
+        <v>416</v>
+      </c>
+      <c r="C355" t="n">
+        <v>785673</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>127</v>
+      </c>
+      <c r="B356" t="s">
+        <v>416</v>
+      </c>
+      <c r="C356" t="n">
+        <v>658110</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>127</v>
+      </c>
+      <c r="B357" t="s">
+        <v>417</v>
+      </c>
+      <c r="C357" t="n">
+        <v>412713</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>128</v>
+      </c>
+      <c r="B358" t="s">
+        <v>415</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>128</v>
+      </c>
+      <c r="B359" t="s">
+        <v>416</v>
+      </c>
+      <c r="C359" t="n">
+        <v>20040</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>128</v>
+      </c>
+      <c r="B360" t="s">
+        <v>417</v>
+      </c>
+      <c r="C360" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>129</v>
+      </c>
+      <c r="B361" t="s">
+        <v>416</v>
+      </c>
+      <c r="C361" t="n">
+        <v>93000</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>129</v>
+      </c>
+      <c r="B362" t="s">
+        <v>417</v>
+      </c>
+      <c r="C362" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>130</v>
+      </c>
+      <c r="B363" t="s">
+        <v>417</v>
+      </c>
+      <c r="C363" t="n">
+        <v>301671</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>131</v>
+      </c>
+      <c r="B364" t="s">
+        <v>415</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>131</v>
+      </c>
+      <c r="B365" t="s">
+        <v>417</v>
+      </c>
+      <c r="C365" t="n">
+        <v>7459281</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>132</v>
+      </c>
+      <c r="B366" t="s">
+        <v>415</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>132</v>
+      </c>
+      <c r="B367" t="s">
+        <v>416</v>
+      </c>
+      <c r="C367" t="n">
+        <v>547119</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>133</v>
+      </c>
+      <c r="B368" t="s">
+        <v>416</v>
+      </c>
+      <c r="C368" t="n">
+        <v>155220</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>134</v>
+      </c>
+      <c r="B369" t="s">
+        <v>416</v>
+      </c>
+      <c r="C369" t="n">
+        <v>112920</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>135</v>
+      </c>
+      <c r="B370" t="s">
+        <v>416</v>
+      </c>
+      <c r="C370" t="n">
+        <v>8445771</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>136</v>
+      </c>
+      <c r="B371" t="s">
+        <v>416</v>
+      </c>
+      <c r="C371" t="n">
+        <v>296460</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>137</v>
+      </c>
+      <c r="B372" t="s">
+        <v>416</v>
+      </c>
+      <c r="C372" t="n">
+        <v>417639</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>137</v>
+      </c>
+      <c r="B373" t="s">
+        <v>417</v>
+      </c>
+      <c r="C373" t="n">
+        <v>173730</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>138</v>
+      </c>
+      <c r="B374" t="s">
+        <v>416</v>
+      </c>
+      <c r="C374" t="n">
+        <v>36120</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>139</v>
+      </c>
+      <c r="B375" t="s">
+        <v>416</v>
+      </c>
+      <c r="C375" t="n">
+        <v>580233</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>140</v>
+      </c>
+      <c r="B376" t="s">
+        <v>416</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1167120</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>141</v>
+      </c>
+      <c r="B377" t="s">
+        <v>416</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1003077</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>142</v>
+      </c>
+      <c r="B378" t="s">
+        <v>416</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1191750</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>143</v>
+      </c>
+      <c r="B379" t="s">
+        <v>415</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>143</v>
+      </c>
+      <c r="B380" t="s">
+        <v>417</v>
+      </c>
+      <c r="C380" t="n">
+        <v>594327</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>144</v>
+      </c>
+      <c r="B381" t="s">
+        <v>417</v>
+      </c>
+      <c r="C381" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>145</v>
+      </c>
+      <c r="B382" t="s">
+        <v>416</v>
+      </c>
+      <c r="C382" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>146</v>
+      </c>
+      <c r="B383" t="s">
+        <v>416</v>
+      </c>
+      <c r="C383" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>147</v>
+      </c>
+      <c r="B384" t="s">
+        <v>418</v>
+      </c>
+      <c r="C384" t="n">
+        <v>71592</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>147</v>
+      </c>
+      <c r="B385" t="s">
+        <v>415</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>147</v>
+      </c>
+      <c r="B386" t="s">
+        <v>416</v>
+      </c>
+      <c r="C386" t="n">
+        <v>4755723</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>147</v>
+      </c>
+      <c r="B387" t="s">
+        <v>420</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>147</v>
+      </c>
+      <c r="B388" t="s">
+        <v>417</v>
+      </c>
+      <c r="C388" t="n">
+        <v>115847961</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>148</v>
+      </c>
+      <c r="B389" t="s">
+        <v>418</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1546209</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>148</v>
+      </c>
+      <c r="B390" t="s">
+        <v>415</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>148</v>
+      </c>
+      <c r="B391" t="s">
+        <v>416</v>
+      </c>
+      <c r="C391" t="n">
+        <v>3020931</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>148</v>
+      </c>
+      <c r="B392" t="s">
+        <v>420</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>148</v>
+      </c>
+      <c r="B393" t="s">
+        <v>417</v>
+      </c>
+      <c r="C393" t="n">
+        <v>64070688</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>149</v>
+      </c>
+      <c r="B394" t="s">
+        <v>418</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1042776</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>149</v>
+      </c>
+      <c r="B395" t="s">
+        <v>415</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>149</v>
+      </c>
+      <c r="B396" t="s">
+        <v>416</v>
+      </c>
+      <c r="C396" t="n">
+        <v>3467613</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>149</v>
+      </c>
+      <c r="B397" t="s">
+        <v>420</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>149</v>
+      </c>
+      <c r="B398" t="s">
+        <v>417</v>
+      </c>
+      <c r="C398" t="n">
+        <v>12219822</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>150</v>
+      </c>
+      <c r="B399" t="s">
+        <v>418</v>
+      </c>
+      <c r="C399" t="n">
+        <v>11910459</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>150</v>
+      </c>
+      <c r="B400" t="s">
+        <v>415</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>150</v>
+      </c>
+      <c r="B401" t="s">
+        <v>416</v>
+      </c>
+      <c r="C401" t="n">
+        <v>49030770</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>150</v>
+      </c>
+      <c r="B402" t="s">
+        <v>419</v>
+      </c>
+      <c r="C402" t="n">
+        <v>374604</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>150</v>
+      </c>
+      <c r="B403" t="s">
+        <v>420</v>
+      </c>
+      <c r="C403" t="n">
+        <v>433119</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>150</v>
+      </c>
+      <c r="B404" t="s">
+        <v>417</v>
+      </c>
+      <c r="C404" t="n">
+        <v>228235929</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>151</v>
+      </c>
+      <c r="B405" t="s">
+        <v>418</v>
+      </c>
+      <c r="C405" t="n">
+        <v>19024002</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>151</v>
+      </c>
+      <c r="B406" t="s">
+        <v>415</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>151</v>
+      </c>
+      <c r="B407" t="s">
+        <v>416</v>
+      </c>
+      <c r="C407" t="n">
+        <v>30780</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>151</v>
+      </c>
+      <c r="B408" t="s">
+        <v>419</v>
+      </c>
+      <c r="C408" t="n">
+        <v>43022961</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>151</v>
+      </c>
+      <c r="B409" t="s">
+        <v>420</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>151</v>
+      </c>
+      <c r="B410" t="s">
+        <v>417</v>
+      </c>
+      <c r="C410" t="n">
+        <v>673195542</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>152</v>
+      </c>
+      <c r="B411" t="s">
+        <v>418</v>
+      </c>
+      <c r="C411" t="n">
+        <v>7695492</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>152</v>
+      </c>
+      <c r="B412" t="s">
+        <v>415</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>152</v>
+      </c>
+      <c r="B413" t="s">
+        <v>416</v>
+      </c>
+      <c r="C413" t="n">
+        <v>2749884</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>152</v>
+      </c>
+      <c r="B414" t="s">
+        <v>420</v>
+      </c>
+      <c r="C414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>152</v>
+      </c>
+      <c r="B415" t="s">
+        <v>417</v>
+      </c>
+      <c r="C415" t="n">
+        <v>60610446</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>153</v>
+      </c>
+      <c r="B416" t="s">
+        <v>418</v>
+      </c>
+      <c r="C416" t="n">
+        <v>357401775</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>153</v>
+      </c>
+      <c r="B417" t="s">
+        <v>415</v>
+      </c>
+      <c r="C417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>153</v>
+      </c>
+      <c r="B418" t="s">
+        <v>416</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1063992</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>153</v>
+      </c>
+      <c r="B419" t="s">
+        <v>419</v>
+      </c>
+      <c r="C419" t="n">
+        <v>22944750</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>153</v>
+      </c>
+      <c r="B420" t="s">
+        <v>417</v>
+      </c>
+      <c r="C420" t="n">
+        <v>2829532248</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>154</v>
+      </c>
+      <c r="B421" t="s">
+        <v>418</v>
+      </c>
+      <c r="C421" t="n">
+        <v>36327546</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>154</v>
+      </c>
+      <c r="B422" t="s">
+        <v>415</v>
+      </c>
+      <c r="C422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>154</v>
+      </c>
+      <c r="B423" t="s">
+        <v>419</v>
+      </c>
+      <c r="C423" t="n">
+        <v>8981619</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>154</v>
+      </c>
+      <c r="B424" t="s">
+        <v>420</v>
+      </c>
+      <c r="C424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>154</v>
+      </c>
+      <c r="B425" t="s">
+        <v>417</v>
+      </c>
+      <c r="C425" t="n">
+        <v>146293980</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>155</v>
+      </c>
+      <c r="B426" t="s">
+        <v>415</v>
+      </c>
+      <c r="C426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>155</v>
+      </c>
+      <c r="B427" t="s">
+        <v>417</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1162458</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>156</v>
+      </c>
+      <c r="B428" t="s">
+        <v>415</v>
+      </c>
+      <c r="C428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>156</v>
+      </c>
+      <c r="B429" t="s">
+        <v>416</v>
+      </c>
+      <c r="C429" t="n">
+        <v>87960</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>156</v>
+      </c>
+      <c r="B430" t="s">
+        <v>417</v>
+      </c>
+      <c r="C430" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>157</v>
+      </c>
+      <c r="B431" t="s">
+        <v>415</v>
+      </c>
+      <c r="C431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>157</v>
+      </c>
+      <c r="B432" t="s">
+        <v>417</v>
+      </c>
+      <c r="C432" t="n">
+        <v>21040680</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>158</v>
+      </c>
+      <c r="B433" t="s">
+        <v>417</v>
+      </c>
+      <c r="C433" t="n">
+        <v>188220</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>159</v>
+      </c>
+      <c r="B434" t="s">
+        <v>415</v>
+      </c>
+      <c r="C434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>159</v>
+      </c>
+      <c r="B435" t="s">
+        <v>417</v>
+      </c>
+      <c r="C435" t="n">
+        <v>119008734</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>160</v>
+      </c>
+      <c r="B436" t="s">
+        <v>418</v>
+      </c>
+      <c r="C436" t="n">
+        <v>30003</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>160</v>
+      </c>
+      <c r="B437" t="s">
+        <v>416</v>
+      </c>
+      <c r="C437" t="n">
+        <v>828987</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>160</v>
+      </c>
+      <c r="B438" t="s">
+        <v>417</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1916541</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>161</v>
+      </c>
+      <c r="B439" t="s">
+        <v>418</v>
+      </c>
+      <c r="C439" t="n">
+        <v>10166061</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>161</v>
+      </c>
+      <c r="B440" t="s">
+        <v>415</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>161</v>
+      </c>
+      <c r="B441" t="s">
+        <v>416</v>
+      </c>
+      <c r="C441" t="n">
+        <v>709608</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>161</v>
+      </c>
+      <c r="B442" t="s">
+        <v>417</v>
+      </c>
+      <c r="C442" t="n">
+        <v>360603360</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>162</v>
+      </c>
+      <c r="B443" t="s">
+        <v>416</v>
+      </c>
+      <c r="C443" t="n">
+        <v>444264</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>162</v>
+      </c>
+      <c r="B444" t="s">
+        <v>417</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1033911</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>163</v>
+      </c>
+      <c r="B445" t="s">
+        <v>417</v>
+      </c>
+      <c r="C445" t="n">
+        <v>434328</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>164</v>
+      </c>
+      <c r="B446" t="s">
+        <v>418</v>
+      </c>
+      <c r="C446" t="n">
+        <v>34825368</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>164</v>
+      </c>
+      <c r="B447" t="s">
+        <v>415</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>164</v>
+      </c>
+      <c r="B448" t="s">
+        <v>417</v>
+      </c>
+      <c r="C448" t="n">
+        <v>335633562</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>165</v>
+      </c>
+      <c r="B449" t="s">
+        <v>417</v>
+      </c>
+      <c r="C449" t="n">
+        <v>15258786</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>166</v>
+      </c>
+      <c r="B450" t="s">
+        <v>416</v>
+      </c>
+      <c r="C450" t="n">
+        <v>139110</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>167</v>
+      </c>
+      <c r="B451" t="s">
+        <v>418</v>
+      </c>
+      <c r="C451" t="n">
+        <v>844158</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>167</v>
+      </c>
+      <c r="B452" t="s">
+        <v>415</v>
+      </c>
+      <c r="C452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>167</v>
+      </c>
+      <c r="B453" t="s">
+        <v>416</v>
+      </c>
+      <c r="C453" t="n">
+        <v>338400</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>168</v>
+      </c>
+      <c r="B454" t="s">
+        <v>418</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1752531</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>168</v>
+      </c>
+      <c r="B455" t="s">
+        <v>415</v>
+      </c>
+      <c r="C455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>168</v>
+      </c>
+      <c r="B456" t="s">
+        <v>417</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1515369</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>169</v>
+      </c>
+      <c r="B457" t="s">
+        <v>418</v>
+      </c>
+      <c r="C457" t="n">
+        <v>21012</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>169</v>
+      </c>
+      <c r="B458" t="s">
+        <v>415</v>
+      </c>
+      <c r="C458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>170</v>
+      </c>
+      <c r="B459" t="s">
+        <v>418</v>
+      </c>
+      <c r="C459" t="n">
+        <v>22375584</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>170</v>
+      </c>
+      <c r="B460" t="s">
+        <v>415</v>
+      </c>
+      <c r="C460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>170</v>
+      </c>
+      <c r="B461" t="s">
+        <v>417</v>
+      </c>
+      <c r="C461" t="n">
+        <v>9246396</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>171</v>
+      </c>
+      <c r="B462" t="s">
+        <v>418</v>
+      </c>
+      <c r="C462" t="n">
+        <v>26342463</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>171</v>
+      </c>
+      <c r="B463" t="s">
+        <v>415</v>
+      </c>
+      <c r="C463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>172</v>
+      </c>
+      <c r="B464" t="s">
+        <v>418</v>
+      </c>
+      <c r="C464" t="n">
+        <v>74561448</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>172</v>
+      </c>
+      <c r="B465" t="s">
+        <v>415</v>
+      </c>
+      <c r="C465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>173</v>
+      </c>
+      <c r="B466" t="s">
+        <v>417</v>
+      </c>
+      <c r="C466" t="n">
+        <v>6771711</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>174</v>
+      </c>
+      <c r="B467" t="s">
+        <v>418</v>
+      </c>
+      <c r="C467" t="n">
+        <v>78384</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>174</v>
+      </c>
+      <c r="B468" t="s">
+        <v>415</v>
+      </c>
+      <c r="C468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>174</v>
+      </c>
+      <c r="B469" t="s">
+        <v>416</v>
+      </c>
+      <c r="C469" t="n">
+        <v>47488794</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>174</v>
+      </c>
+      <c r="B470" t="s">
+        <v>417</v>
+      </c>
+      <c r="C470" t="n">
+        <v>26319366</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>175</v>
+      </c>
+      <c r="B471" t="s">
+        <v>416</v>
+      </c>
+      <c r="C471" t="n">
+        <v>222690</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>175</v>
+      </c>
+      <c r="B472" t="s">
+        <v>417</v>
+      </c>
+      <c r="C472" t="n">
+        <v>296976</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>176</v>
+      </c>
+      <c r="B473" t="s">
+        <v>418</v>
+      </c>
+      <c r="C473" t="n">
+        <v>3737097</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>176</v>
+      </c>
+      <c r="B474" t="s">
+        <v>415</v>
+      </c>
+      <c r="C474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>176</v>
+      </c>
+      <c r="B475" t="s">
+        <v>416</v>
+      </c>
+      <c r="C475" t="n">
+        <v>38273979</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>176</v>
+      </c>
+      <c r="B476" t="s">
+        <v>420</v>
+      </c>
+      <c r="C476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>176</v>
+      </c>
+      <c r="B477" t="s">
+        <v>417</v>
+      </c>
+      <c r="C477" t="n">
+        <v>32067687</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>177</v>
+      </c>
+      <c r="B478" t="s">
+        <v>418</v>
+      </c>
+      <c r="C478" t="n">
+        <v>1132359</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>177</v>
+      </c>
+      <c r="B479" t="s">
+        <v>415</v>
+      </c>
+      <c r="C479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>177</v>
+      </c>
+      <c r="B480" t="s">
+        <v>416</v>
+      </c>
+      <c r="C480" t="n">
+        <v>6434718</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>177</v>
+      </c>
+      <c r="B481" t="s">
+        <v>417</v>
+      </c>
+      <c r="C481" t="n">
+        <v>2984133</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>178</v>
+      </c>
+      <c r="B482" t="s">
+        <v>418</v>
+      </c>
+      <c r="C482" t="n">
+        <v>3088227</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>178</v>
+      </c>
+      <c r="B483" t="s">
+        <v>415</v>
+      </c>
+      <c r="C483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>178</v>
+      </c>
+      <c r="B484" t="s">
+        <v>416</v>
+      </c>
+      <c r="C484" t="n">
+        <v>2671770</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>178</v>
+      </c>
+      <c r="B485" t="s">
+        <v>419</v>
+      </c>
+      <c r="C485" t="n">
+        <v>149125770</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>178</v>
+      </c>
+      <c r="B486" t="s">
+        <v>417</v>
+      </c>
+      <c r="C486" t="n">
+        <v>73789638</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>179</v>
+      </c>
+      <c r="B487" t="s">
+        <v>415</v>
+      </c>
+      <c r="C487" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>179</v>
+      </c>
+      <c r="B488" t="s">
+        <v>416</v>
+      </c>
+      <c r="C488" t="n">
+        <v>2428959</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>179</v>
+      </c>
+      <c r="B489" t="s">
+        <v>417</v>
+      </c>
+      <c r="C489" t="n">
+        <v>380277441</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>180</v>
+      </c>
+      <c r="B490" t="s">
+        <v>416</v>
+      </c>
+      <c r="C490" t="n">
+        <v>56070</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>74034345</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>336561</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80989818</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>35571126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24382686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10900233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9666921</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>308505360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>38667261</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>17759586</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1054835961</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="n">
+        <v>33980520</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>37401</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70755</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="n">
+        <v>149917293</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="n">
+        <v>597741</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="n">
+        <v>208008891</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="n">
+        <v>721083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="n">
+        <v>376023</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5015526</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="n">
+        <v>908379</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="n">
+        <v>376329</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5876694</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="n">
+        <v>118283523</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="n">
+        <v>21480</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="n">
+        <v>53727522</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="n">
+        <v>233309979</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="n">
+        <v>66332097</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="n">
+        <v>243846</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91261542</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="n">
+        <v>55755303</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="n">
+        <v>25275795</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="n">
+        <v>84316386</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="n">
+        <v>239490</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78191133</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7788552</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="n">
+        <v>45912936</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101052354</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8390046</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="n">
+        <v>35719854</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="n">
+        <v>33422985</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106584</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="n">
+        <v>233985</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="n">
+        <v>16869426</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="n">
+        <v>199653960</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114461</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="n">
+        <v>22117392</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="n">
+        <v>868290</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="n">
+        <v>27606900</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" t="n">
+        <v>741501</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="n">
+        <v>22004841</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="n">
+        <v>76932276</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5831688</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="n">
+        <v>306774</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="n">
+        <v>837969</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3504000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" t="n">
+        <v>13571469</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" t="n">
+        <v>25423446</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" t="n">
+        <v>25604964</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4878918</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" t="n">
+        <v>35269146</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" t="n">
+        <v>827478</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2413746</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="n">
+        <v>21270</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1515462</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" t="n">
+        <v>421626</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" t="n">
+        <v>314754663</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2383044</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" t="n">
+        <v>642382644</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" t="n">
+        <v>33010260</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5328543</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" t="n">
+        <v>11652</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="n">
+        <v>77859</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" t="n">
+        <v>19169424</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="n">
+        <v>35253933</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" t="n">
+        <v>13108761</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="n">
+        <v>19416669</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="n">
+        <v>939954</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" t="n">
+        <v>12607248</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" t="n">
+        <v>5775549</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" t="n">
+        <v>214527</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" t="n">
+        <v>428190</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5098137</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" t="n">
+        <v>15360321</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8409024</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" t="n">
+        <v>25569024</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" t="n">
+        <v>745758</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n">
+        <v>60655191</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n">
+        <v>11901462</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" t="n">
+        <v>67200</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" t="n">
+        <v>177225537</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" t="n">
+        <v>439680</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" t="n">
+        <v>852113022</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="n">
+        <v>6926112</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9905757</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" t="n">
+        <v>28781982</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="n">
+        <v>575199</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="n">
+        <v>47247789</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" t="n">
+        <v>22636830</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" t="n">
+        <v>50057526</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" t="n">
+        <v>39819363</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="n">
+        <v>31341888</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" t="n">
+        <v>7374303</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1480032</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" t="n">
+        <v>762969747</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" t="n">
+        <v>21018276</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1084140</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="n">
+        <v>46744653</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" t="n">
+        <v>69929292</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" t="n">
+        <v>4628073</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" t="n">
+        <v>6602322</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" t="n">
+        <v>9295833</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" t="n">
+        <v>11265333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" t="n">
+        <v>7524816</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1148100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" t="n">
+        <v>47220129</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" t="n">
+        <v>139800</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" t="n">
+        <v>24244239</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" t="n">
+        <v>772692</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1337655</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" t="n">
+        <v>785673</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1070823</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" t="n">
+        <v>20073</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" t="n">
+        <v>93006</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="n">
+        <v>301671</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" t="n">
+        <v>7459281</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" t="n">
+        <v>547119</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" t="n">
+        <v>155220</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133" t="n">
+        <v>112920</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" t="n">
+        <v>8445771</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="n">
+        <v>296460</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" t="n">
+        <v>591369</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137" t="n">
+        <v>36120</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" t="n">
+        <v>580233</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1167120</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1003077</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1191750</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>594327</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" t="n">
+        <v>120675276</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>148</v>
+      </c>
+      <c r="B147" t="n">
+        <v>68637828</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" t="n">
+        <v>16730211</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" t="n">
+        <v>289984881</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" t="n">
+        <v>735273285</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" t="n">
+        <v>71055822</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3210942765</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" t="n">
+        <v>191603145</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1162458</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" t="n">
+        <v>87963</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="n">
+        <v>21040680</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B157" t="n">
+        <v>188220</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>159</v>
+      </c>
+      <c r="B158" t="n">
+        <v>119008734</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>160</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2775531</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160" t="n">
+        <v>371479029</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>162</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1478175</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162" t="n">
+        <v>434328</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>164</v>
+      </c>
+      <c r="B163" t="n">
+        <v>370458930</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164" t="n">
+        <v>15258786</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>166</v>
+      </c>
+      <c r="B165" t="n">
+        <v>139110</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>167</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1182558</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3267900</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168" t="n">
+        <v>21012</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169" t="n">
+        <v>31621980</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170" t="n">
+        <v>26342463</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>172</v>
+      </c>
+      <c r="B171" t="n">
+        <v>74561448</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172" t="n">
+        <v>6771711</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>174</v>
+      </c>
+      <c r="B173" t="n">
+        <v>73886544</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174" t="n">
+        <v>519666</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175" t="n">
+        <v>74078763</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176" t="n">
+        <v>10551210</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" t="n">
+        <v>228675405</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178" t="n">
+        <v>382706400</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179" t="n">
+        <v>56070</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>